--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -548,7 +548,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>28854.55</v>
+        <v>28830.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18.41</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1567.330255296035</v>
+        <v>1567.748776508972</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.131881959321549</v>
+        <v>0.1319361967180483</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05431830526887561</v>
+        <v>0.0543773790103317</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>72.7527837286196</v>
+        <v>72.77447868721934</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>90.23492602767679</v>
+        <v>90.24143451525671</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40499.81379684953</v>
+        <v>40510.62838499185</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.4035850081477454</v>
+        <v>0.4051114736269712</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>31.79115907776754</v>
+        <v>31.79170300137243</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49827.24547351424</v>
+        <v>49841.40348353825</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.726841883637563</v>
+        <v>0.7287494834895285</v>
       </c>
     </row>
     <row r="15"/>
@@ -4205,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4296,6 +4296,39 @@
       </c>
       <c r="I2">
         <f>IF(H2="","",IF(H2&gt;=70,"BUY",IF(H2&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="18" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>28830.9</v>
+      </c>
+      <c r="C3" s="7" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E3" s="8" t="n">
+        <v>0.131936196718</v>
+      </c>
+      <c r="F3" s="22">
+        <f>IF(D3="","",100*(1-D3))</f>
+        <v/>
+      </c>
+      <c r="G3" s="22">
+        <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H3" s="22">
+        <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
+        <v/>
+      </c>
+      <c r="I3">
+        <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -567,7 +567,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>28830.9</v>
+        <v>28582.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="E5" s="7" t="n">
-        <v>18.39</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="6">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1567.748776508972</v>
+        <v>1567.86066922655</v>
       </c>
     </row>
     <row r="7">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>0.1319361967180483</v>
+        <v>0.132388104246566</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0543773790103317</v>
+        <v>0.05485463521667581</v>
       </c>
     </row>
     <row r="8">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="E8" s="11" t="n">
-        <v>72.77447868721934</v>
+        <v>72.95524169862639</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>90.24143451525671</v>
+        <v>90.29566341867883</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -720,10 +720,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40510.62838499185</v>
+        <v>40513.51969281404</v>
       </c>
       <c r="D13" s="16" t="n">
-        <v>0.4051114736269712</v>
+        <v>0.417443773998903</v>
       </c>
     </row>
     <row r="14">
@@ -733,13 +733,13 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>31.79170300137243</v>
+        <v>31.79623498830128</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49841.40348353825</v>
+        <v>49852.06626764267</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>0.7287494834895285</v>
+        <v>0.7441708715469706</v>
       </c>
     </row>
     <row r="15"/>
@@ -4205,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4329,6 +4329,39 @@
       </c>
       <c r="I3">
         <f>IF(H3="","",IF(H3&gt;=70,"BUY",IF(H3&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="18" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>28582.1</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.132388104247</v>
+      </c>
+      <c r="F4" s="22">
+        <f>IF(D4="","",100*(1-D4))</f>
+        <v/>
+      </c>
+      <c r="G4" s="22">
+        <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H4" s="22">
+        <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
+        <v/>
+      </c>
+      <c r="I4">
+        <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Monthly PE History" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Quarterly Backtest" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Score History" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sources &amp; Methodology" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Composition" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Sources &amp; Methodology" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,17 +21,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00;[Red](#,##0.00);-"/>
-    <numFmt numFmtId="167" formatCode="0.00x;[Red](0.00x);-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0.0;[Red](#,##0.0);-"/>
-    <numFmt numFmtId="170" formatCode="0.0"/>
-    <numFmt numFmtId="171" formatCode="0.00x"/>
+  <numFmts count="7">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.00x;[Red](0.00x);-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +67,11 @@
       <color theme="10"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="15"/>
     </font>
   </fonts>
   <fills count="5">
@@ -105,36 +110,53 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -566,7 +588,7 @@
           <t>As of</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="23" t="n">
         <v>46287</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -580,7 +602,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
@@ -594,7 +615,7 @@
           <t>Index level</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>28582.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -602,7 +623,7 @@
           <t>P/E</t>
         </is>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="25" t="n">
         <v>18.23</v>
       </c>
     </row>
@@ -612,7 +633,7 @@
           <t>P/E percentile</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n">
+      <c r="B6" s="26" t="n">
         <v>0.02272727272727273</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -620,7 +641,7 @@
           <t>Implied EPS</t>
         </is>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="27" t="n">
         <v>1567.86066922655</v>
       </c>
     </row>
@@ -630,7 +651,7 @@
           <t>YoY implied EPS growth</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n">
+      <c r="B7" s="26" t="n">
         <v>0.132388104246566</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -648,7 +669,7 @@
           <t>Valuation score</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="28" t="n">
         <v>97.72727272727273</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -656,7 +677,7 @@
           <t>Growth score</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="28" t="n">
         <v>72.95524169862639</v>
       </c>
     </row>
@@ -666,7 +687,7 @@
           <t>Composite score</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n">
+      <c r="B9" s="28" t="n">
         <v>90.29566341867883</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -680,7 +701,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
@@ -716,13 +736,13 @@
           <t>BUY → HOLD</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
+      <c r="B13" s="29" t="n">
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
         <v>40513.51969281404</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="30" t="n">
         <v>0.417443773998903</v>
       </c>
     </row>
@@ -732,17 +752,16 @@
           <t>HOLD → SELL</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
+      <c r="B14" s="29" t="n">
         <v>31.79623498830128</v>
       </c>
       <c r="C14" s="15" t="n">
         <v>49852.06626764267</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="30" t="n">
         <v>0.7441708715469706</v>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
@@ -796,17 +815,17 @@
       <c r="B18" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="16" t="n">
+      <c r="C18" s="30" t="n">
         <v>0.1780224341809005</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="D18" s="30" t="n">
         <v>0.1460220480377938</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="E18" s="30" t="n">
         <v>0.2570055415900238</v>
       </c>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="16" t="n">
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -819,19 +838,19 @@
       <c r="B19" t="n">
         <v>8</v>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.2195443637358583</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.1081782378754973</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.210513148963401</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.08989068682106849</v>
       </c>
-      <c r="G19" s="16" t="n">
+      <c r="G19" s="30" t="n">
         <v>0.125</v>
       </c>
     </row>
@@ -844,19 +863,19 @@
       <c r="B20" t="n">
         <v>9</v>
       </c>
-      <c r="C20" s="16" t="n">
+      <c r="C20" s="30" t="n">
         <v>0.09775659523541291</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="D20" s="30" t="n">
         <v>0.1138441081150927</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="E20" s="30" t="n">
         <v>0.179836325853753</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="F20" s="30" t="n">
         <v>0.1142257588523116</v>
       </c>
-      <c r="G20" s="16" t="n">
+      <c r="G20" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -869,17 +888,17 @@
       <c r="B21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="30" t="n">
         <v>0.1115554678272994</v>
       </c>
-      <c r="D21" s="16" t="n">
+      <c r="D21" s="30" t="n">
         <v>0.2228452356411557</v>
       </c>
-      <c r="E21" s="16" t="n">
+      <c r="E21" s="30" t="n">
         <v>0.1972011370042706</v>
       </c>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="16" t="n">
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -892,21 +911,20 @@
       <c r="B22" t="n">
         <v>10</v>
       </c>
-      <c r="C22" s="16" t="n">
+      <c r="C22" s="30" t="n">
         <v>-0.15456822960026</v>
       </c>
-      <c r="D22" s="16" t="n">
+      <c r="D22" s="30" t="n">
         <v>0.1517614731882273</v>
       </c>
-      <c r="E22" s="16" t="n">
+      <c r="E22" s="30" t="n">
         <v>0.1494827586704077</v>
       </c>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="16" t="n">
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="30" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
@@ -1042,16 +1060,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>44316</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>25664.45</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>27.99</v>
       </c>
-      <c r="D2" s="19">
+      <c r="D2" s="32">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
@@ -1061,16 +1079,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>44347</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>27115.05</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>29.35</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="32">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
@@ -1080,16 +1098,16 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>29168</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>31.87</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="32">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
@@ -1099,16 +1117,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>44408</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>30480.05</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>31.78</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="32">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
@@ -1118,16 +1136,16 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>44439</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>34570.2</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>35.66</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="32">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
@@ -1137,16 +1155,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>35028</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>36.81</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="32">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
@@ -1156,16 +1174,16 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>44500</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>34408.75</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>34.63</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="32">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
@@ -1175,16 +1193,16 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>44530</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>35043.75</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>35.27</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="32">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
@@ -1194,16 +1212,16 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>38701</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>38.91</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="32">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
@@ -1213,16 +1231,16 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>44592</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>34824.55</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>34.38</v>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="32">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
@@ -1232,16 +1250,16 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>44620</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>33847.85</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>33.35</v>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="32">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
@@ -1251,16 +1269,16 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>36317.2</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>35.85</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="32">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
@@ -1270,16 +1288,16 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>44681</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>31622.4</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>29.93</v>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="32">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
@@ -1289,16 +1307,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>44712</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>29679.05</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>27.65</v>
       </c>
-      <c r="D15" s="19">
+      <c r="D15" s="32">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
@@ -1308,16 +1326,16 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>27843.35</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>25.39</v>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="32">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
@@ -1327,16 +1345,16 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>44773</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>29152.3</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>26.54</v>
       </c>
-      <c r="D17" s="19">
+      <c r="D17" s="32">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
@@ -1346,16 +1364,16 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>44804</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>28407.9</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>25.84</v>
       </c>
-      <c r="D18" s="19">
+      <c r="D18" s="32">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
@@ -1365,16 +1383,16 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>26981.15</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>24.72</v>
       </c>
-      <c r="D19" s="19">
+      <c r="D19" s="32">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
@@ -1384,16 +1402,16 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44865</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>28727.6</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>25.84</v>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="32">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
@@ -1403,16 +1421,16 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44895</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>30391.7</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>27.3</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="32">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
@@ -1422,16 +1440,16 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>28621.7</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>26.29</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="32">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
@@ -1441,16 +1459,16 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44957</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>29740.35</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>26.35</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="32">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
@@ -1460,16 +1478,16 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44985</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>29663.95</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>26.28</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="32">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
@@ -1479,16 +1497,16 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>28698.6</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>25.31</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="32">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
@@ -1498,16 +1516,16 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>45046</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>27708.2</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="32">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
@@ -1517,16 +1535,16 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>45077</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>29319.75</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>25.5</v>
       </c>
-      <c r="D27" s="19">
+      <c r="D27" s="32">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
@@ -1536,16 +1554,16 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>29563</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>25.42</v>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="32">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
@@ -1555,16 +1573,16 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>29928.45</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>25.17</v>
       </c>
-      <c r="D29" s="19">
+      <c r="D29" s="32">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
@@ -1574,16 +1592,16 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>45169</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>31164.9</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>26.21</v>
       </c>
-      <c r="D30" s="19">
+      <c r="D30" s="32">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
@@ -1593,16 +1611,16 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>31784.4</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>26.74</v>
       </c>
-      <c r="D31" s="19">
+      <c r="D31" s="32">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
@@ -1612,16 +1630,16 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45230</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>30582.25</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>25.75</v>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="32">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
@@ -1631,16 +1649,16 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45260</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>32582.2</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>27.43</v>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="32">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
@@ -1650,16 +1668,16 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>35515</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>29.74</v>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="32">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
@@ -1669,16 +1687,16 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45322</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>36638.4</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>31.32</v>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="32">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
@@ -1688,16 +1706,16 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45351</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>37720.4</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>32.26</v>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="32">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
@@ -1707,16 +1725,16 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>34898.15</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>29.93</v>
       </c>
-      <c r="D37" s="19">
+      <c r="D37" s="32">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
@@ -1726,16 +1744,16 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45412</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>33200.95</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>27.98</v>
       </c>
-      <c r="D38" s="19">
+      <c r="D38" s="32">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
@@ -1745,16 +1763,16 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45443</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>32386.1</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>27.19</v>
       </c>
-      <c r="D39" s="19">
+      <c r="D39" s="32">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
@@ -1764,16 +1782,16 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>36157.5</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>30.25</v>
       </c>
-      <c r="D40" s="19">
+      <c r="D40" s="32">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
@@ -1783,16 +1801,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45504</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>40851.1</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>33.38</v>
       </c>
-      <c r="D41" s="19">
+      <c r="D41" s="32">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
@@ -1802,16 +1820,16 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>45535</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>42787.8</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>34.97</v>
       </c>
-      <c r="D42" s="19">
+      <c r="D42" s="32">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
@@ -1821,16 +1839,16 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>41946.05</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>34.4</v>
       </c>
-      <c r="D43" s="19">
+      <c r="D43" s="32">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
@@ -1840,16 +1858,16 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>45596</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>40407.55</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>31.99</v>
       </c>
-      <c r="D44" s="19">
+      <c r="D44" s="32">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
@@ -1859,16 +1877,16 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="n">
+      <c r="A45" s="31" t="n">
         <v>45626</v>
       </c>
-      <c r="B45" s="6" t="n">
+      <c r="B45" s="24" t="n">
         <v>43146.25</v>
       </c>
-      <c r="C45" s="7" t="n">
+      <c r="C45" s="25" t="n">
         <v>34.15</v>
       </c>
-      <c r="D45" s="19">
+      <c r="D45" s="32">
         <f>IFERROR(B45/C45,"")</f>
         <v/>
       </c>
@@ -1878,16 +1896,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="n">
+      <c r="A46" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B46" s="6" t="n">
+      <c r="B46" s="24" t="n">
         <v>43337.8</v>
       </c>
-      <c r="C46" s="7" t="n">
+      <c r="C46" s="25" t="n">
         <v>34.03</v>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="32">
         <f>IFERROR(B46/C46,"")</f>
         <v/>
       </c>
@@ -1897,16 +1915,16 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="n">
+      <c r="A47" s="31" t="n">
         <v>45688</v>
       </c>
-      <c r="B47" s="6" t="n">
+      <c r="B47" s="24" t="n">
         <v>42662.75</v>
       </c>
-      <c r="C47" s="7" t="n">
+      <c r="C47" s="25" t="n">
         <v>32.33</v>
       </c>
-      <c r="D47" s="19">
+      <c r="D47" s="32">
         <f>IFERROR(B47/C47,"")</f>
         <v/>
       </c>
@@ -1916,16 +1934,16 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="n">
+      <c r="A48" s="31" t="n">
         <v>45716</v>
       </c>
-      <c r="B48" s="6" t="n">
+      <c r="B48" s="24" t="n">
         <v>37318.3</v>
       </c>
-      <c r="C48" s="7" t="n">
+      <c r="C48" s="25" t="n">
         <v>28.28</v>
       </c>
-      <c r="D48" s="19">
+      <c r="D48" s="32">
         <f>IFERROR(B48/C48,"")</f>
         <v/>
       </c>
@@ -1935,16 +1953,16 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="n">
+      <c r="A49" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B49" s="6" t="n">
+      <c r="B49" s="24" t="n">
         <v>36886.15</v>
       </c>
-      <c r="C49" s="7" t="n">
+      <c r="C49" s="25" t="n">
         <v>27.87</v>
       </c>
-      <c r="D49" s="19">
+      <c r="D49" s="32">
         <f>IFERROR(B49/C49,"")</f>
         <v/>
       </c>
@@ -1954,16 +1972,16 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="n">
+      <c r="A50" s="31" t="n">
         <v>45777</v>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B50" s="24" t="n">
         <v>35794.95</v>
       </c>
-      <c r="C50" s="7" t="n">
+      <c r="C50" s="25" t="n">
         <v>26.85</v>
       </c>
-      <c r="D50" s="19">
+      <c r="D50" s="32">
         <f>IFERROR(B50/C50,"")</f>
         <v/>
       </c>
@@ -1973,16 +1991,16 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="n">
+      <c r="A51" s="31" t="n">
         <v>45808</v>
       </c>
-      <c r="B51" s="6" t="n">
+      <c r="B51" s="24" t="n">
         <v>37321.75</v>
       </c>
-      <c r="C51" s="7" t="n">
+      <c r="C51" s="25" t="n">
         <v>27.89</v>
       </c>
-      <c r="D51" s="19">
+      <c r="D51" s="32">
         <f>IFERROR(B51/C51,"")</f>
         <v/>
       </c>
@@ -1992,16 +2010,16 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="n">
+      <c r="A52" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B52" s="6" t="n">
+      <c r="B52" s="24" t="n">
         <v>38950</v>
       </c>
-      <c r="C52" s="7" t="n">
+      <c r="C52" s="25" t="n">
         <v>28.81</v>
       </c>
-      <c r="D52" s="19">
+      <c r="D52" s="32">
         <f>IFERROR(B52/C52,"")</f>
         <v/>
       </c>
@@ -2011,16 +2029,16 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="n">
+      <c r="A53" s="31" t="n">
         <v>45869</v>
       </c>
-      <c r="B53" s="6" t="n">
+      <c r="B53" s="24" t="n">
         <v>35301.6</v>
       </c>
-      <c r="C53" s="7" t="n">
+      <c r="C53" s="25" t="n">
         <v>25.49</v>
       </c>
-      <c r="D53" s="19">
+      <c r="D53" s="32">
         <f>IFERROR(B53/C53,"")</f>
         <v/>
       </c>
@@ -2030,16 +2048,16 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="n">
+      <c r="A54" s="31" t="n">
         <v>45900</v>
       </c>
-      <c r="B54" s="6" t="n">
+      <c r="B54" s="24" t="n">
         <v>35181.25</v>
       </c>
-      <c r="C54" s="7" t="n">
+      <c r="C54" s="25" t="n">
         <v>25.41</v>
       </c>
-      <c r="D54" s="19">
+      <c r="D54" s="32">
         <f>IFERROR(B54/C54,"")</f>
         <v/>
       </c>
@@ -2049,16 +2067,16 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="n">
+      <c r="A55" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B55" s="6" t="n">
+      <c r="B55" s="24" t="n">
         <v>33655.1</v>
       </c>
-      <c r="C55" s="7" t="n">
+      <c r="C55" s="25" t="n">
         <v>24.29</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="32">
         <f>IFERROR(B55/C55,"")</f>
         <v/>
       </c>
@@ -2068,16 +2086,16 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="n">
+      <c r="A56" s="31" t="n">
         <v>45961</v>
       </c>
-      <c r="B56" s="6" t="n">
+      <c r="B56" s="24" t="n">
         <v>35712.35</v>
       </c>
-      <c r="C56" s="7" t="n">
+      <c r="C56" s="25" t="n">
         <v>25.31</v>
       </c>
-      <c r="D56" s="19">
+      <c r="D56" s="32">
         <f>IFERROR(B56/C56,"")</f>
         <v/>
       </c>
@@ -2087,16 +2105,16 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="n">
+      <c r="A57" s="31" t="n">
         <v>45991</v>
       </c>
-      <c r="B57" s="6" t="n">
+      <c r="B57" s="24" t="n">
         <v>37405.5</v>
       </c>
-      <c r="C57" s="7" t="n">
+      <c r="C57" s="25" t="n">
         <v>26.49</v>
       </c>
-      <c r="D57" s="19">
+      <c r="D57" s="32">
         <f>IFERROR(B57/C57,"")</f>
         <v/>
       </c>
@@ -2106,16 +2124,16 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="n">
+      <c r="A58" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B58" s="6" t="n">
+      <c r="B58" s="24" t="n">
         <v>37884.05</v>
       </c>
-      <c r="C58" s="7" t="n">
+      <c r="C58" s="25" t="n">
         <v>26.65</v>
       </c>
-      <c r="D58" s="19">
+      <c r="D58" s="32">
         <f>IFERROR(B58/C58,"")</f>
         <v/>
       </c>
@@ -2125,16 +2143,16 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="n">
+      <c r="A59" s="31" t="n">
         <v>46053</v>
       </c>
-      <c r="B59" s="6" t="n">
+      <c r="B59" s="24" t="n">
         <v>38036.15</v>
       </c>
-      <c r="C59" s="7" t="n">
+      <c r="C59" s="25" t="n">
         <v>27.03</v>
       </c>
-      <c r="D59" s="19">
+      <c r="D59" s="32">
         <f>IFERROR(B59/C59,"")</f>
         <v/>
       </c>
@@ -2144,16 +2162,16 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="n">
+      <c r="A60" s="31" t="n">
         <v>46081</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B60" s="24" t="n">
         <v>30603.85</v>
       </c>
-      <c r="C60" s="7" t="n">
+      <c r="C60" s="25" t="n">
         <v>21.74</v>
       </c>
-      <c r="D60" s="19">
+      <c r="D60" s="32">
         <f>IFERROR(B60/C60,"")</f>
         <v/>
       </c>
@@ -2163,16 +2181,16 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="n">
+      <c r="A61" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B61" s="6" t="n">
+      <c r="B61" s="24" t="n">
         <v>29062.6</v>
       </c>
-      <c r="C61" s="7" t="n">
+      <c r="C61" s="25" t="n">
         <v>20.64</v>
       </c>
-      <c r="D61" s="19">
+      <c r="D61" s="32">
         <f>IFERROR(B61/C61,"")</f>
         <v/>
       </c>
@@ -2182,16 +2200,16 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="n">
+      <c r="A62" s="31" t="n">
         <v>46142</v>
       </c>
-      <c r="B62" s="6" t="n">
+      <c r="B62" s="24" t="n">
         <v>29353.9</v>
       </c>
-      <c r="C62" s="7" t="n">
+      <c r="C62" s="25" t="n">
         <v>20.15</v>
       </c>
-      <c r="D62" s="19">
+      <c r="D62" s="32">
         <f>IFERROR(B62/C62,"")</f>
         <v/>
       </c>
@@ -2201,16 +2219,16 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="n">
+      <c r="A63" s="31" t="n">
         <v>46173</v>
       </c>
-      <c r="B63" s="6" t="n">
+      <c r="B63" s="24" t="n">
         <v>29080.15</v>
       </c>
-      <c r="C63" s="7" t="n">
+      <c r="C63" s="25" t="n">
         <v>19.79</v>
       </c>
-      <c r="D63" s="19">
+      <c r="D63" s="32">
         <f>IFERROR(B63/C63,"")</f>
         <v/>
       </c>
@@ -2220,16 +2238,16 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="n">
+      <c r="A64" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B64" s="6" t="n">
+      <c r="B64" s="24" t="n">
         <v>26299.05</v>
       </c>
-      <c r="C64" s="7" t="n">
+      <c r="C64" s="25" t="n">
         <v>17.26</v>
       </c>
-      <c r="D64" s="19">
+      <c r="D64" s="32">
         <f>IFERROR(B64/C64,"")</f>
         <v/>
       </c>
@@ -2239,16 +2257,16 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="n">
+      <c r="A65" s="31" t="n">
         <v>46234</v>
       </c>
-      <c r="B65" s="6" t="n">
+      <c r="B65" s="24" t="n">
         <v>30708.9</v>
       </c>
-      <c r="C65" s="7" t="n">
+      <c r="C65" s="25" t="n">
         <v>19.61</v>
       </c>
-      <c r="D65" s="19">
+      <c r="D65" s="32">
         <f>IFERROR(B65/C65,"")</f>
         <v/>
       </c>
@@ -2258,16 +2276,16 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="n">
+      <c r="A66" s="31" t="n">
         <v>46265</v>
       </c>
-      <c r="B66" s="6" t="n">
+      <c r="B66" s="24" t="n">
         <v>31191.45</v>
       </c>
-      <c r="C66" s="7" t="n">
+      <c r="C66" s="25" t="n">
         <v>19.9</v>
       </c>
-      <c r="D66" s="19">
+      <c r="D66" s="32">
         <f>IFERROR(B66/C66,"")</f>
         <v/>
       </c>
@@ -2369,13 +2387,13 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>42369</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>11212.55</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>19.51</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2383,12 +2401,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E2" s="21">
+      <c r="E2" s="33">
         <f>IFERROR(B2/C2,"")</f>
         <v/>
       </c>
-      <c r="F2" s="16" t="n"/>
-      <c r="G2" s="16">
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30">
         <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2396,31 +2414,31 @@
         <f>IF(G2="","",IF(G2&lt;=20%,"Q1 Cheapest",IF(G2&lt;=40%,"Q2",IF(G2&lt;=60%,"Q3",IF(G2&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I2" s="16">
+      <c r="I2" s="30">
         <f>IFERROR(B6/B2-1,"")</f>
         <v/>
       </c>
-      <c r="J2" s="16">
+      <c r="J2" s="30">
         <f>IFERROR((B14/B2)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K2" s="16">
+      <c r="K2" s="30">
         <f>IFERROR((B22/B2)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L2" s="16">
+      <c r="L2" s="30">
         <f>IFERROR((B42/B2)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>42460</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>11309.3</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>19.71</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -2428,12 +2446,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="33">
         <f>IFERROR(B3/C3,"")</f>
         <v/>
       </c>
-      <c r="F3" s="16" t="n"/>
-      <c r="G3" s="16">
+      <c r="F3" s="30" t="n"/>
+      <c r="G3" s="30">
         <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2441,31 +2459,31 @@
         <f>IF(G3="","",IF(G3&lt;=20%,"Q1 Cheapest",IF(G3&lt;=40%,"Q2",IF(G3&lt;=60%,"Q3",IF(G3&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I3" s="16">
+      <c r="I3" s="30">
         <f>IFERROR(B7/B3-1,"")</f>
         <v/>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="30">
         <f>IFERROR((B15/B3)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="30">
         <f>IFERROR((B23/B3)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="30">
         <f>IFERROR((B43/B3)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>42551</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>11120.15</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>18.49</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -2473,12 +2491,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E4" s="21">
+      <c r="E4" s="33">
         <f>IFERROR(B4/C4,"")</f>
         <v/>
       </c>
-      <c r="F4" s="16" t="n"/>
-      <c r="G4" s="16">
+      <c r="F4" s="30" t="n"/>
+      <c r="G4" s="30">
         <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2486,31 +2504,31 @@
         <f>IF(G4="","",IF(G4&lt;=20%,"Q1 Cheapest",IF(G4&lt;=40%,"Q2",IF(G4&lt;=60%,"Q3",IF(G4&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I4" s="16">
+      <c r="I4" s="30">
         <f>IFERROR(B8/B4-1,"")</f>
         <v/>
       </c>
-      <c r="J4" s="16">
+      <c r="J4" s="30">
         <f>IFERROR((B16/B4)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K4" s="16">
+      <c r="K4" s="30">
         <f>IFERROR((B24/B4)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="30">
         <f>IFERROR((B44/B4)^(1/10)-1,"")</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
+      <c r="A5" s="31" t="n">
         <v>42643</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="24" t="n">
         <v>10292.3</v>
       </c>
-      <c r="C5" s="7" t="n">
+      <c r="C5" s="25" t="n">
         <v>16.67</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -2518,12 +2536,12 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="33">
         <f>IFERROR(B5/C5,"")</f>
         <v/>
       </c>
-      <c r="F5" s="16" t="n"/>
-      <c r="G5" s="16">
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30">
         <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2531,28 +2549,28 @@
         <f>IF(G5="","",IF(G5&lt;=20%,"Q1 Cheapest",IF(G5&lt;=40%,"Q2",IF(G5&lt;=60%,"Q3",IF(G5&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="30">
         <f>IFERROR(B9/B5-1,"")</f>
         <v/>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="30">
         <f>IFERROR((B17/B5)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K5" s="16">
+      <c r="K5" s="30">
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="16" t="n"/>
+      <c r="L5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
+      <c r="A6" s="31" t="n">
         <v>42735</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="24" t="n">
         <v>10399.25</v>
       </c>
-      <c r="C6" s="7" t="n">
+      <c r="C6" s="25" t="n">
         <v>16.63</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2560,15 +2578,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="33">
         <f>IFERROR(B6/C6,"")</f>
         <v/>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="30">
         <f>IF(AND(D6=D2,E2&lt;&gt;""),E6/E2-1,"")</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="30">
         <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2576,28 +2594,28 @@
         <f>IF(G6="","",IF(G6&lt;=20%,"Q1 Cheapest",IF(G6&lt;=40%,"Q2",IF(G6&lt;=60%,"Q3",IF(G6&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I6" s="16">
+      <c r="I6" s="30">
         <f>IFERROR(B10/B6-1,"")</f>
         <v/>
       </c>
-      <c r="J6" s="16">
+      <c r="J6" s="30">
         <f>IFERROR((B18/B6)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K6" s="16">
+      <c r="K6" s="30">
         <f>IFERROR((B26/B6)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L6" s="16" t="n"/>
+      <c r="L6" s="30" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
+      <c r="A7" s="31" t="n">
         <v>42825</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="24" t="n">
         <v>10703.25</v>
       </c>
-      <c r="C7" s="7" t="n">
+      <c r="C7" s="25" t="n">
         <v>16.92</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2605,15 +2623,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="33">
         <f>IFERROR(B7/C7,"")</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="30">
         <f>IF(AND(D7=D3,E3&lt;&gt;""),E7/E3-1,"")</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="30">
         <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2621,28 +2639,28 @@
         <f>IF(G7="","",IF(G7&lt;=20%,"Q1 Cheapest",IF(G7&lt;=40%,"Q2",IF(G7&lt;=60%,"Q3",IF(G7&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="30">
         <f>IFERROR(B11/B7-1,"")</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="30">
         <f>IFERROR((B19/B7)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="30">
         <f>IFERROR((B27/B7)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L7" s="16" t="n"/>
+      <c r="L7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
+      <c r="A8" s="31" t="n">
         <v>42916</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="24" t="n">
         <v>10155.05</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="25" t="n">
         <v>16.38</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2650,15 +2668,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="33">
         <f>IFERROR(B8/C8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="30">
         <f>IF(AND(D8=D4,E4&lt;&gt;""),E8/E4-1,"")</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="30">
         <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2666,28 +2684,28 @@
         <f>IF(G8="","",IF(G8&lt;=20%,"Q1 Cheapest",IF(G8&lt;=40%,"Q2",IF(G8&lt;=60%,"Q3",IF(G8&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I8" s="16">
+      <c r="I8" s="30">
         <f>IFERROR(B12/B8-1,"")</f>
         <v/>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="30">
         <f>IFERROR((B20/B8)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K8" s="16">
+      <c r="K8" s="30">
         <f>IFERROR((B28/B8)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L8" s="16" t="n"/>
+      <c r="L8" s="30" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
+      <c r="A9" s="31" t="n">
         <v>43008</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="24" t="n">
         <v>10475.35</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="25" t="n">
         <v>16.95</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2695,15 +2713,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="33">
         <f>IFERROR(B9/C9,"")</f>
         <v/>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="30">
         <f>IF(AND(D9=D5,E5&lt;&gt;""),E9/E5-1,"")</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="30">
         <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2711,28 +2729,28 @@
         <f>IF(G9="","",IF(G9&lt;=20%,"Q1 Cheapest",IF(G9&lt;=40%,"Q2",IF(G9&lt;=60%,"Q3",IF(G9&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I9" s="16">
+      <c r="I9" s="30">
         <f>IFERROR(B13/B9-1,"")</f>
         <v/>
       </c>
-      <c r="J9" s="16">
+      <c r="J9" s="30">
         <f>IFERROR((B21/B9)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K9" s="16">
+      <c r="K9" s="30">
         <f>IFERROR((B29/B9)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L9" s="16" t="n"/>
+      <c r="L9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="n">
+      <c r="A10" s="31" t="n">
         <v>43100</v>
       </c>
-      <c r="B10" s="6" t="n">
+      <c r="B10" s="24" t="n">
         <v>11665.75</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="25" t="n">
         <v>18.45</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2740,15 +2758,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="33">
         <f>IFERROR(B10/C10,"")</f>
         <v/>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="30">
         <f>IF(AND(D10=D6,E6&lt;&gt;""),E10/E6-1,"")</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="30">
         <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2756,28 +2774,28 @@
         <f>IF(G10="","",IF(G10&lt;=20%,"Q1 Cheapest",IF(G10&lt;=40%,"Q2",IF(G10&lt;=60%,"Q3",IF(G10&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="30">
         <f>IFERROR(B14/B10-1,"")</f>
         <v/>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="30">
         <f>IFERROR((B22/B10)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="30">
         <f>IFERROR((B30/B10)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L10" s="16" t="n"/>
+      <c r="L10" s="30" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="n">
+      <c r="A11" s="31" t="n">
         <v>43190</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="24" t="n">
         <v>12511.55</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="25" t="n">
         <v>18.58</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2785,15 +2803,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="33">
         <f>IFERROR(B11/C11,"")</f>
         <v/>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="30">
         <f>IF(AND(D11=D7,E7&lt;&gt;""),E11/E7-1,"")</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="30">
         <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2801,28 +2819,28 @@
         <f>IF(G11="","",IF(G11&lt;=20%,"Q1 Cheapest",IF(G11&lt;=40%,"Q2",IF(G11&lt;=60%,"Q3",IF(G11&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I11" s="16">
+      <c r="I11" s="30">
         <f>IFERROR(B15/B11-1,"")</f>
         <v/>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="30">
         <f>IFERROR((B23/B11)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K11" s="16">
+      <c r="K11" s="30">
         <f>IFERROR((B31/B11)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L11" s="16" t="n"/>
+      <c r="L11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="n">
+      <c r="A12" s="31" t="n">
         <v>43281</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="24" t="n">
         <v>13989.5</v>
       </c>
-      <c r="C12" s="7" t="n">
+      <c r="C12" s="25" t="n">
         <v>19.95</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2830,15 +2848,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="33">
         <f>IFERROR(B12/C12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="30">
         <f>IF(AND(D12=D8,E8&lt;&gt;""),E12/E8-1,"")</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="30">
         <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2846,28 +2864,28 @@
         <f>IF(G12="","",IF(G12&lt;=20%,"Q1 Cheapest",IF(G12&lt;=40%,"Q2",IF(G12&lt;=60%,"Q3",IF(G12&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I12" s="16">
+      <c r="I12" s="30">
         <f>IFERROR(B16/B12-1,"")</f>
         <v/>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="30">
         <f>IFERROR((B24/B12)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K12" s="16">
+      <c r="K12" s="30">
         <f>IFERROR((B32/B12)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L12" s="16" t="n"/>
+      <c r="L12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="n">
+      <c r="A13" s="31" t="n">
         <v>43373</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="24" t="n">
         <v>15838.05</v>
       </c>
-      <c r="C13" s="7" t="n">
+      <c r="C13" s="25" t="n">
         <v>22.25</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2875,15 +2893,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="33">
         <f>IFERROR(B13/C13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="30">
         <f>IF(AND(D13=D9,E9&lt;&gt;""),E13/E9-1,"")</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="30">
         <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2891,28 +2909,28 @@
         <f>IF(G13="","",IF(G13&lt;=20%,"Q1 Cheapest",IF(G13&lt;=40%,"Q2",IF(G13&lt;=60%,"Q3",IF(G13&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="30">
         <f>IFERROR(B17/B13-1,"")</f>
         <v/>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="30">
         <f>IFERROR((B25/B13)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="30">
         <f>IFERROR((B33/B13)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L13" s="16" t="n"/>
+      <c r="L13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="n">
+      <c r="A14" s="31" t="n">
         <v>43465</v>
       </c>
-      <c r="B14" s="6" t="n">
+      <c r="B14" s="24" t="n">
         <v>14440.3</v>
       </c>
-      <c r="C14" s="7" t="n">
+      <c r="C14" s="25" t="n">
         <v>20</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2920,15 +2938,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E14" s="21">
+      <c r="E14" s="33">
         <f>IFERROR(B14/C14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="30">
         <f>IF(AND(D14=D10,E10&lt;&gt;""),E14/E10-1,"")</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="30">
         <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2936,28 +2954,28 @@
         <f>IF(G14="","",IF(G14&lt;=20%,"Q1 Cheapest",IF(G14&lt;=40%,"Q2",IF(G14&lt;=60%,"Q3",IF(G14&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I14" s="16">
+      <c r="I14" s="30">
         <f>IFERROR(B18/B14-1,"")</f>
         <v/>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="30">
         <f>IFERROR((B26/B14)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K14" s="16">
+      <c r="K14" s="30">
         <f>IFERROR((B34/B14)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L14" s="16" t="n"/>
+      <c r="L14" s="30" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="n">
+      <c r="A15" s="31" t="n">
         <v>43555</v>
       </c>
-      <c r="B15" s="6" t="n">
+      <c r="B15" s="24" t="n">
         <v>15628.2</v>
       </c>
-      <c r="C15" s="7" t="n">
+      <c r="C15" s="25" t="n">
         <v>23.27</v>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2965,15 +2983,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E15" s="21">
+      <c r="E15" s="33">
         <f>IFERROR(B15/C15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="30">
         <f>IF(AND(D15=D11,E11&lt;&gt;""),E15/E11-1,"")</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="30">
         <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -2981,28 +2999,28 @@
         <f>IF(G15="","",IF(G15&lt;=20%,"Q1 Cheapest",IF(G15&lt;=40%,"Q2",IF(G15&lt;=60%,"Q3",IF(G15&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="30">
         <f>IFERROR(B19/B15-1,"")</f>
         <v/>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="30">
         <f>IFERROR((B27/B15)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="30">
         <f>IFERROR((B35/B15)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L15" s="16" t="n"/>
+      <c r="L15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="n">
+      <c r="A16" s="31" t="n">
         <v>43646</v>
       </c>
-      <c r="B16" s="6" t="n">
+      <c r="B16" s="24" t="n">
         <v>15936.45</v>
       </c>
-      <c r="C16" s="7" t="n">
+      <c r="C16" s="25" t="n">
         <v>23.13</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3010,15 +3028,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E16" s="21">
+      <c r="E16" s="33">
         <f>IFERROR(B16/C16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="30">
         <f>IF(AND(D16=D12,E12&lt;&gt;""),E16/E12-1,"")</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="30">
         <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3026,28 +3044,28 @@
         <f>IF(G16="","",IF(G16&lt;=20%,"Q1 Cheapest",IF(G16&lt;=40%,"Q2",IF(G16&lt;=60%,"Q3",IF(G16&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I16" s="16">
+      <c r="I16" s="30">
         <f>IFERROR(B20/B16-1,"")</f>
         <v/>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="30">
         <f>IFERROR((B28/B16)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K16" s="16">
+      <c r="K16" s="30">
         <f>IFERROR((B36/B16)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L16" s="16" t="n"/>
+      <c r="L16" s="30" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="n">
+      <c r="A17" s="31" t="n">
         <v>43738</v>
       </c>
-      <c r="B17" s="6" t="n">
+      <c r="B17" s="24" t="n">
         <v>15540.15</v>
       </c>
-      <c r="C17" s="7" t="n">
+      <c r="C17" s="25" t="n">
         <v>21.16</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3055,15 +3073,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="33">
         <f>IFERROR(B17/C17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="30">
         <f>IF(AND(D17=D13,E13&lt;&gt;""),E17/E13-1,"")</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="30">
         <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3071,28 +3089,28 @@
         <f>IF(G17="","",IF(G17&lt;=20%,"Q1 Cheapest",IF(G17&lt;=40%,"Q2",IF(G17&lt;=60%,"Q3",IF(G17&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I17" s="16">
+      <c r="I17" s="30">
         <f>IFERROR(B21/B17-1,"")</f>
         <v/>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="30">
         <f>IFERROR((B29/B17)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K17" s="16">
+      <c r="K17" s="30">
         <f>IFERROR((B37/B17)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L17" s="16" t="n"/>
+      <c r="L17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="n">
+      <c r="A18" s="31" t="n">
         <v>43830</v>
       </c>
-      <c r="B18" s="6" t="n">
+      <c r="B18" s="24" t="n">
         <v>15652.4</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C18" s="25" t="n">
         <v>20.66</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3100,15 +3118,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E18" s="21">
+      <c r="E18" s="33">
         <f>IFERROR(B18/C18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="30">
         <f>IF(AND(D18=D14,E14&lt;&gt;""),E18/E14-1,"")</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="30">
         <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3116,28 +3134,28 @@
         <f>IF(G18="","",IF(G18&lt;=20%,"Q1 Cheapest",IF(G18&lt;=40%,"Q2",IF(G18&lt;=60%,"Q3",IF(G18&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="30">
         <f>IFERROR(B22/B18-1,"")</f>
         <v/>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="30">
         <f>IFERROR((B30/B18)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K18" s="16">
+      <c r="K18" s="30">
         <f>IFERROR((B38/B18)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L18" s="16" t="n"/>
+      <c r="L18" s="30" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="n">
+      <c r="A19" s="31" t="n">
         <v>43921</v>
       </c>
-      <c r="B19" s="6" t="n">
+      <c r="B19" s="24" t="n">
         <v>12763.65</v>
       </c>
-      <c r="C19" s="7" t="n">
+      <c r="C19" s="25" t="n">
         <v>16.56</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -3145,15 +3163,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="33">
         <f>IFERROR(B19/C19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="30">
         <f>IF(AND(D19=D15,E15&lt;&gt;""),E19/E15-1,"")</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="30">
         <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3161,28 +3179,28 @@
         <f>IF(G19="","",IF(G19&lt;=20%,"Q1 Cheapest",IF(G19&lt;=40%,"Q2",IF(G19&lt;=60%,"Q3",IF(G19&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I19" s="16">
+      <c r="I19" s="30">
         <f>IFERROR(B23/B19-1,"")</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="30">
         <f>IFERROR((B31/B19)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="30">
         <f>IFERROR((B39/B19)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L19" s="16" t="n"/>
+      <c r="L19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="n">
+      <c r="A20" s="31" t="n">
         <v>44012</v>
       </c>
-      <c r="B20" s="6" t="n">
+      <c r="B20" s="24" t="n">
         <v>14754.3</v>
       </c>
-      <c r="C20" s="7" t="n">
+      <c r="C20" s="25" t="n">
         <v>19.67</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -3190,15 +3208,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="33">
         <f>IFERROR(B20/C20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="16">
+      <c r="F20" s="30">
         <f>IF(AND(D20=D16,E16&lt;&gt;""),E20/E16-1,"")</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="30">
         <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3206,28 +3224,28 @@
         <f>IF(G20="","",IF(G20&lt;=20%,"Q1 Cheapest",IF(G20&lt;=40%,"Q2",IF(G20&lt;=60%,"Q3",IF(G20&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="30">
         <f>IFERROR(B24/B20-1,"")</f>
         <v/>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="30">
         <f>IFERROR((B32/B20)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K20" s="16">
+      <c r="K20" s="30">
         <f>IFERROR((B40/B20)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L20" s="16" t="n"/>
+      <c r="L20" s="30" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n">
+      <c r="A21" s="31" t="n">
         <v>44104</v>
       </c>
-      <c r="B21" s="6" t="n">
+      <c r="B21" s="24" t="n">
         <v>19951.3</v>
       </c>
-      <c r="C21" s="7" t="n">
+      <c r="C21" s="25" t="n">
         <v>26.86</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3235,15 +3253,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E21" s="21">
+      <c r="E21" s="33">
         <f>IFERROR(B21/C21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="16">
+      <c r="F21" s="30">
         <f>IF(AND(D21=D17,E17&lt;&gt;""),E21/E17-1,"")</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="30">
         <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3251,28 +3269,28 @@
         <f>IF(G21="","",IF(G21&lt;=20%,"Q1 Cheapest",IF(G21&lt;=40%,"Q2",IF(G21&lt;=60%,"Q3",IF(G21&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I21" s="16">
+      <c r="I21" s="30">
         <f>IFERROR(B25/B21-1,"")</f>
         <v/>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="30">
         <f>IFERROR((B33/B21)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K21" s="16">
+      <c r="K21" s="30">
         <f>IFERROR((B41/B21)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L21" s="16" t="n"/>
+      <c r="L21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="n">
+      <c r="A22" s="31" t="n">
         <v>44196</v>
       </c>
-      <c r="B22" s="6" t="n">
+      <c r="B22" s="24" t="n">
         <v>24251.35</v>
       </c>
-      <c r="C22" s="7" t="n">
+      <c r="C22" s="25" t="n">
         <v>32.69</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -3280,15 +3298,15 @@
           <t>Standalone</t>
         </is>
       </c>
-      <c r="E22" s="21">
+      <c r="E22" s="33">
         <f>IFERROR(B22/C22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="16">
+      <c r="F22" s="30">
         <f>IF(AND(D22=D18,E18&lt;&gt;""),E22/E18-1,"")</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="30">
         <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3296,28 +3314,28 @@
         <f>IF(G22="","",IF(G22&lt;=20%,"Q1 Cheapest",IF(G22&lt;=40%,"Q2",IF(G22&lt;=60%,"Q3",IF(G22&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I22" s="16">
+      <c r="I22" s="30">
         <f>IFERROR(B26/B22-1,"")</f>
         <v/>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="30">
         <f>IFERROR((B34/B22)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K22" s="16">
+      <c r="K22" s="30">
         <f>IFERROR((B42/B22)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L22" s="16" t="n"/>
+      <c r="L22" s="30" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="n">
+      <c r="A23" s="31" t="n">
         <v>44286</v>
       </c>
-      <c r="B23" s="6" t="n">
+      <c r="B23" s="24" t="n">
         <v>25855</v>
       </c>
-      <c r="C23" s="7" t="n">
+      <c r="C23" s="25" t="n">
         <v>28.65</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -3325,15 +3343,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="33">
         <f>IFERROR(B23/C23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="30">
         <f>IF(AND(D23=D19,E19&lt;&gt;""),E23/E19-1,"")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="30">
         <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3341,28 +3359,28 @@
         <f>IF(G23="","",IF(G23&lt;=20%,"Q1 Cheapest",IF(G23&lt;=40%,"Q2",IF(G23&lt;=60%,"Q3",IF(G23&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="30">
         <f>IFERROR(B27/B23-1,"")</f>
         <v/>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="30">
         <f>IFERROR((B35/B23)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K23" s="16">
+      <c r="K23" s="30">
         <f>IFERROR((B43/B23)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L23" s="16" t="n"/>
+      <c r="L23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="n">
+      <c r="A24" s="31" t="n">
         <v>44377</v>
       </c>
-      <c r="B24" s="6" t="n">
+      <c r="B24" s="24" t="n">
         <v>29168</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="C24" s="25" t="n">
         <v>31.87</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3370,15 +3388,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="33">
         <f>IFERROR(B24/C24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="30">
         <f>IF(AND(D24=D20,E20&lt;&gt;""),E24/E20-1,"")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="30">
         <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3386,28 +3404,28 @@
         <f>IF(G24="","",IF(G24&lt;=20%,"Q1 Cheapest",IF(G24&lt;=40%,"Q2",IF(G24&lt;=60%,"Q3",IF(G24&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="30">
         <f>IFERROR(B28/B24-1,"")</f>
         <v/>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="30">
         <f>IFERROR((B36/B24)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K24" s="16">
+      <c r="K24" s="30">
         <f>IFERROR((B44/B24)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L24" s="16" t="n"/>
+      <c r="L24" s="30" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="n">
+      <c r="A25" s="31" t="n">
         <v>44469</v>
       </c>
-      <c r="B25" s="6" t="n">
+      <c r="B25" s="24" t="n">
         <v>35028</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="C25" s="25" t="n">
         <v>36.81</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -3415,15 +3433,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E25" s="21">
+      <c r="E25" s="33">
         <f>IFERROR(B25/C25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="30">
         <f>IF(AND(D25=D21,E21&lt;&gt;""),E25/E21-1,"")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="30">
         <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3431,25 +3449,25 @@
         <f>IF(G25="","",IF(G25&lt;=20%,"Q1 Cheapest",IF(G25&lt;=40%,"Q2",IF(G25&lt;=60%,"Q3",IF(G25&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="30">
         <f>IFERROR(B29/B25-1,"")</f>
         <v/>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="30">
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="16" t="n"/>
-      <c r="L25" s="16" t="n"/>
+      <c r="K25" s="30" t="n"/>
+      <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="n">
+      <c r="A26" s="31" t="n">
         <v>44561</v>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B26" s="24" t="n">
         <v>38701</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C26" s="25" t="n">
         <v>38.91</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -3457,15 +3475,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E26" s="21">
+      <c r="E26" s="33">
         <f>IFERROR(B26/C26,"")</f>
         <v/>
       </c>
-      <c r="F26" s="16">
+      <c r="F26" s="30">
         <f>IF(AND(D26=D22,E22&lt;&gt;""),E26/E22-1,"")</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="30">
         <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3473,25 +3491,25 @@
         <f>IF(G26="","",IF(G26&lt;=20%,"Q1 Cheapest",IF(G26&lt;=40%,"Q2",IF(G26&lt;=60%,"Q3",IF(G26&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I26" s="16">
+      <c r="I26" s="30">
         <f>IFERROR(B30/B26-1,"")</f>
         <v/>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="30">
         <f>IFERROR((B38/B26)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K26" s="16" t="n"/>
-      <c r="L26" s="16" t="n"/>
+      <c r="K26" s="30" t="n"/>
+      <c r="L26" s="30" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="n">
+      <c r="A27" s="31" t="n">
         <v>44651</v>
       </c>
-      <c r="B27" s="6" t="n">
+      <c r="B27" s="24" t="n">
         <v>36317.2</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C27" s="25" t="n">
         <v>35.85</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -3499,15 +3517,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E27" s="21">
+      <c r="E27" s="33">
         <f>IFERROR(B27/C27,"")</f>
         <v/>
       </c>
-      <c r="F27" s="16">
+      <c r="F27" s="30">
         <f>IF(AND(D27=D23,E23&lt;&gt;""),E27/E23-1,"")</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="30">
         <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3515,25 +3533,25 @@
         <f>IF(G27="","",IF(G27&lt;=20%,"Q1 Cheapest",IF(G27&lt;=40%,"Q2",IF(G27&lt;=60%,"Q3",IF(G27&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="30">
         <f>IFERROR(B31/B27-1,"")</f>
         <v/>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="30">
         <f>IFERROR((B39/B27)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K27" s="16" t="n"/>
-      <c r="L27" s="16" t="n"/>
+      <c r="K27" s="30" t="n"/>
+      <c r="L27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="n">
+      <c r="A28" s="31" t="n">
         <v>44742</v>
       </c>
-      <c r="B28" s="6" t="n">
+      <c r="B28" s="24" t="n">
         <v>27843.35</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C28" s="25" t="n">
         <v>25.39</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3541,15 +3559,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E28" s="21">
+      <c r="E28" s="33">
         <f>IFERROR(B28/C28,"")</f>
         <v/>
       </c>
-      <c r="F28" s="16">
+      <c r="F28" s="30">
         <f>IF(AND(D28=D24,E24&lt;&gt;""),E28/E24-1,"")</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="30">
         <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3557,25 +3575,25 @@
         <f>IF(G28="","",IF(G28&lt;=20%,"Q1 Cheapest",IF(G28&lt;=40%,"Q2",IF(G28&lt;=60%,"Q3",IF(G28&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I28" s="16">
+      <c r="I28" s="30">
         <f>IFERROR(B32/B28-1,"")</f>
         <v/>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="30">
         <f>IFERROR((B40/B28)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K28" s="16" t="n"/>
-      <c r="L28" s="16" t="n"/>
+      <c r="K28" s="30" t="n"/>
+      <c r="L28" s="30" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="n">
+      <c r="A29" s="31" t="n">
         <v>44834</v>
       </c>
-      <c r="B29" s="6" t="n">
+      <c r="B29" s="24" t="n">
         <v>26981.15</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="C29" s="25" t="n">
         <v>24.72</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3583,15 +3601,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E29" s="21">
+      <c r="E29" s="33">
         <f>IFERROR(B29/C29,"")</f>
         <v/>
       </c>
-      <c r="F29" s="16">
+      <c r="F29" s="30">
         <f>IF(AND(D29=D25,E25&lt;&gt;""),E29/E25-1,"")</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="30">
         <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3599,25 +3617,25 @@
         <f>IF(G29="","",IF(G29&lt;=20%,"Q1 Cheapest",IF(G29&lt;=40%,"Q2",IF(G29&lt;=60%,"Q3",IF(G29&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="30">
         <f>IFERROR(B33/B29-1,"")</f>
         <v/>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="30">
         <f>IFERROR((B41/B29)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K29" s="16" t="n"/>
-      <c r="L29" s="16" t="n"/>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="n">
+      <c r="A30" s="31" t="n">
         <v>44926</v>
       </c>
-      <c r="B30" s="6" t="n">
+      <c r="B30" s="24" t="n">
         <v>28621.7</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C30" s="25" t="n">
         <v>26.29</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3625,15 +3643,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E30" s="21">
+      <c r="E30" s="33">
         <f>IFERROR(B30/C30,"")</f>
         <v/>
       </c>
-      <c r="F30" s="16">
+      <c r="F30" s="30">
         <f>IF(AND(D30=D26,E26&lt;&gt;""),E30/E26-1,"")</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="30">
         <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3641,25 +3659,25 @@
         <f>IF(G30="","",IF(G30&lt;=20%,"Q1 Cheapest",IF(G30&lt;=40%,"Q2",IF(G30&lt;=60%,"Q3",IF(G30&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="30">
         <f>IFERROR(B34/B30-1,"")</f>
         <v/>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="30">
         <f>IFERROR((B42/B30)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K30" s="16" t="n"/>
-      <c r="L30" s="16" t="n"/>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="n">
+      <c r="A31" s="31" t="n">
         <v>45016</v>
       </c>
-      <c r="B31" s="6" t="n">
+      <c r="B31" s="24" t="n">
         <v>28698.6</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="C31" s="25" t="n">
         <v>25.31</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -3667,15 +3685,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="33">
         <f>IFERROR(B31/C31,"")</f>
         <v/>
       </c>
-      <c r="F31" s="16">
+      <c r="F31" s="30">
         <f>IF(AND(D31=D27,E27&lt;&gt;""),E31/E27-1,"")</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="30">
         <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3683,25 +3701,25 @@
         <f>IF(G31="","",IF(G31&lt;=20%,"Q1 Cheapest",IF(G31&lt;=40%,"Q2",IF(G31&lt;=60%,"Q3",IF(G31&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="30">
         <f>IFERROR(B35/B31-1,"")</f>
         <v/>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="30">
         <f>IFERROR((B43/B31)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K31" s="16" t="n"/>
-      <c r="L31" s="16" t="n"/>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="n">
+      <c r="A32" s="31" t="n">
         <v>45107</v>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B32" s="24" t="n">
         <v>29563</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="C32" s="25" t="n">
         <v>25.42</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -3709,15 +3727,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="33">
         <f>IFERROR(B32/C32,"")</f>
         <v/>
       </c>
-      <c r="F32" s="16">
+      <c r="F32" s="30">
         <f>IF(AND(D32=D28,E28&lt;&gt;""),E32/E28-1,"")</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="30">
         <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3725,25 +3743,25 @@
         <f>IF(G32="","",IF(G32&lt;=20%,"Q1 Cheapest",IF(G32&lt;=40%,"Q2",IF(G32&lt;=60%,"Q3",IF(G32&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="30">
         <f>IFERROR(B36/B32-1,"")</f>
         <v/>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="30">
         <f>IFERROR((B44/B32)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K32" s="16" t="n"/>
-      <c r="L32" s="16" t="n"/>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="n">
+      <c r="A33" s="31" t="n">
         <v>45199</v>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B33" s="24" t="n">
         <v>31784.4</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="C33" s="25" t="n">
         <v>26.74</v>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -3751,15 +3769,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="33">
         <f>IFERROR(B33/C33,"")</f>
         <v/>
       </c>
-      <c r="F33" s="16">
+      <c r="F33" s="30">
         <f>IF(AND(D33=D29,E29&lt;&gt;""),E33/E29-1,"")</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="30">
         <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3767,22 +3785,22 @@
         <f>IF(G33="","",IF(G33&lt;=20%,"Q1 Cheapest",IF(G33&lt;=40%,"Q2",IF(G33&lt;=60%,"Q3",IF(G33&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I33" s="16">
+      <c r="I33" s="30">
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="16" t="n"/>
-      <c r="K33" s="16" t="n"/>
-      <c r="L33" s="16" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="30" t="n"/>
+      <c r="L33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="n">
+      <c r="A34" s="31" t="n">
         <v>45291</v>
       </c>
-      <c r="B34" s="6" t="n">
+      <c r="B34" s="24" t="n">
         <v>35515</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="C34" s="25" t="n">
         <v>29.74</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -3790,15 +3808,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="33">
         <f>IFERROR(B34/C34,"")</f>
         <v/>
       </c>
-      <c r="F34" s="16">
+      <c r="F34" s="30">
         <f>IF(AND(D34=D30,E30&lt;&gt;""),E34/E30-1,"")</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="30">
         <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3806,22 +3824,22 @@
         <f>IF(G34="","",IF(G34&lt;=20%,"Q1 Cheapest",IF(G34&lt;=40%,"Q2",IF(G34&lt;=60%,"Q3",IF(G34&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="30">
         <f>IFERROR(B38/B34-1,"")</f>
         <v/>
       </c>
-      <c r="J34" s="16" t="n"/>
-      <c r="K34" s="16" t="n"/>
-      <c r="L34" s="16" t="n"/>
+      <c r="J34" s="30" t="n"/>
+      <c r="K34" s="30" t="n"/>
+      <c r="L34" s="30" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="n">
+      <c r="A35" s="31" t="n">
         <v>45382</v>
       </c>
-      <c r="B35" s="6" t="n">
+      <c r="B35" s="24" t="n">
         <v>34898.15</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="C35" s="25" t="n">
         <v>29.93</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -3829,15 +3847,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="33">
         <f>IFERROR(B35/C35,"")</f>
         <v/>
       </c>
-      <c r="F35" s="16">
+      <c r="F35" s="30">
         <f>IF(AND(D35=D31,E31&lt;&gt;""),E35/E31-1,"")</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="30">
         <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3845,22 +3863,22 @@
         <f>IF(G35="","",IF(G35&lt;=20%,"Q1 Cheapest",IF(G35&lt;=40%,"Q2",IF(G35&lt;=60%,"Q3",IF(G35&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I35" s="16">
+      <c r="I35" s="30">
         <f>IFERROR(B39/B35-1,"")</f>
         <v/>
       </c>
-      <c r="J35" s="16" t="n"/>
-      <c r="K35" s="16" t="n"/>
-      <c r="L35" s="16" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="30" t="n"/>
+      <c r="L35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="n">
+      <c r="A36" s="31" t="n">
         <v>45473</v>
       </c>
-      <c r="B36" s="6" t="n">
+      <c r="B36" s="24" t="n">
         <v>36157.5</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="C36" s="25" t="n">
         <v>30.25</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3868,15 +3886,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="33">
         <f>IFERROR(B36/C36,"")</f>
         <v/>
       </c>
-      <c r="F36" s="16">
+      <c r="F36" s="30">
         <f>IF(AND(D36=D32,E32&lt;&gt;""),E36/E32-1,"")</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="30">
         <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3884,22 +3902,22 @@
         <f>IF(G36="","",IF(G36&lt;=20%,"Q1 Cheapest",IF(G36&lt;=40%,"Q2",IF(G36&lt;=60%,"Q3",IF(G36&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I36" s="16">
+      <c r="I36" s="30">
         <f>IFERROR(B40/B36-1,"")</f>
         <v/>
       </c>
-      <c r="J36" s="16" t="n"/>
-      <c r="K36" s="16" t="n"/>
-      <c r="L36" s="16" t="n"/>
+      <c r="J36" s="30" t="n"/>
+      <c r="K36" s="30" t="n"/>
+      <c r="L36" s="30" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="n">
+      <c r="A37" s="31" t="n">
         <v>45565</v>
       </c>
-      <c r="B37" s="6" t="n">
+      <c r="B37" s="24" t="n">
         <v>41946.05</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="C37" s="25" t="n">
         <v>34.4</v>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -3907,15 +3925,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E37" s="21">
+      <c r="E37" s="33">
         <f>IFERROR(B37/C37,"")</f>
         <v/>
       </c>
-      <c r="F37" s="16">
+      <c r="F37" s="30">
         <f>IF(AND(D37=D33,E33&lt;&gt;""),E37/E33-1,"")</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="30">
         <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3923,22 +3941,22 @@
         <f>IF(G37="","",IF(G37&lt;=20%,"Q1 Cheapest",IF(G37&lt;=40%,"Q2",IF(G37&lt;=60%,"Q3",IF(G37&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I37" s="16">
+      <c r="I37" s="30">
         <f>IFERROR(B41/B37-1,"")</f>
         <v/>
       </c>
-      <c r="J37" s="16" t="n"/>
-      <c r="K37" s="16" t="n"/>
-      <c r="L37" s="16" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="30" t="n"/>
+      <c r="L37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="n">
+      <c r="A38" s="31" t="n">
         <v>45657</v>
       </c>
-      <c r="B38" s="6" t="n">
+      <c r="B38" s="24" t="n">
         <v>43337.8</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C38" s="25" t="n">
         <v>34.03</v>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -3946,15 +3964,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E38" s="21">
+      <c r="E38" s="33">
         <f>IFERROR(B38/C38,"")</f>
         <v/>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="30">
         <f>IF(AND(D38=D34,E34&lt;&gt;""),E38/E34-1,"")</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="30">
         <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -3962,22 +3980,22 @@
         <f>IF(G38="","",IF(G38&lt;=20%,"Q1 Cheapest",IF(G38&lt;=40%,"Q2",IF(G38&lt;=60%,"Q3",IF(G38&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="30">
         <f>IFERROR(B42/B38-1,"")</f>
         <v/>
       </c>
-      <c r="J38" s="16" t="n"/>
-      <c r="K38" s="16" t="n"/>
-      <c r="L38" s="16" t="n"/>
+      <c r="J38" s="30" t="n"/>
+      <c r="K38" s="30" t="n"/>
+      <c r="L38" s="30" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="n">
+      <c r="A39" s="31" t="n">
         <v>45747</v>
       </c>
-      <c r="B39" s="6" t="n">
+      <c r="B39" s="24" t="n">
         <v>36886.15</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="25" t="n">
         <v>27.87</v>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3985,15 +4003,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="33">
         <f>IFERROR(B39/C39,"")</f>
         <v/>
       </c>
-      <c r="F39" s="16">
+      <c r="F39" s="30">
         <f>IF(AND(D39=D35,E35&lt;&gt;""),E39/E35-1,"")</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="30">
         <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4001,22 +4019,22 @@
         <f>IF(G39="","",IF(G39&lt;=20%,"Q1 Cheapest",IF(G39&lt;=40%,"Q2",IF(G39&lt;=60%,"Q3",IF(G39&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I39" s="16">
+      <c r="I39" s="30">
         <f>IFERROR(B43/B39-1,"")</f>
         <v/>
       </c>
-      <c r="J39" s="16" t="n"/>
-      <c r="K39" s="16" t="n"/>
-      <c r="L39" s="16" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="30" t="n"/>
+      <c r="L39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="n">
+      <c r="A40" s="31" t="n">
         <v>45838</v>
       </c>
-      <c r="B40" s="6" t="n">
+      <c r="B40" s="24" t="n">
         <v>38950</v>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C40" s="25" t="n">
         <v>28.81</v>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -4024,15 +4042,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E40" s="21">
+      <c r="E40" s="33">
         <f>IFERROR(B40/C40,"")</f>
         <v/>
       </c>
-      <c r="F40" s="16">
+      <c r="F40" s="30">
         <f>IF(AND(D40=D36,E36&lt;&gt;""),E40/E36-1,"")</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="30">
         <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4040,22 +4058,22 @@
         <f>IF(G40="","",IF(G40&lt;=20%,"Q1 Cheapest",IF(G40&lt;=40%,"Q2",IF(G40&lt;=60%,"Q3",IF(G40&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I40" s="16">
+      <c r="I40" s="30">
         <f>IFERROR(B44/B40-1,"")</f>
         <v/>
       </c>
-      <c r="J40" s="16" t="n"/>
-      <c r="K40" s="16" t="n"/>
-      <c r="L40" s="16" t="n"/>
+      <c r="J40" s="30" t="n"/>
+      <c r="K40" s="30" t="n"/>
+      <c r="L40" s="30" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="n">
+      <c r="A41" s="31" t="n">
         <v>45930</v>
       </c>
-      <c r="B41" s="6" t="n">
+      <c r="B41" s="24" t="n">
         <v>33655.1</v>
       </c>
-      <c r="C41" s="7" t="n">
+      <c r="C41" s="25" t="n">
         <v>24.29</v>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -4063,15 +4081,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E41" s="21">
+      <c r="E41" s="33">
         <f>IFERROR(B41/C41,"")</f>
         <v/>
       </c>
-      <c r="F41" s="16">
+      <c r="F41" s="30">
         <f>IF(AND(D41=D37,E37&lt;&gt;""),E41/E37-1,"")</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="30">
         <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4079,19 +4097,19 @@
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="16" t="n"/>
-      <c r="J41" s="16" t="n"/>
-      <c r="K41" s="16" t="n"/>
-      <c r="L41" s="16" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="30" t="n"/>
+      <c r="L41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="n">
+      <c r="A42" s="31" t="n">
         <v>46022</v>
       </c>
-      <c r="B42" s="6" t="n">
+      <c r="B42" s="24" t="n">
         <v>37884.05</v>
       </c>
-      <c r="C42" s="7" t="n">
+      <c r="C42" s="25" t="n">
         <v>26.65</v>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -4099,15 +4117,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="33">
         <f>IFERROR(B42/C42,"")</f>
         <v/>
       </c>
-      <c r="F42" s="16">
+      <c r="F42" s="30">
         <f>IF(AND(D42=D38,E38&lt;&gt;""),E42/E38-1,"")</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="30">
         <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4115,19 +4133,19 @@
         <f>IF(G42="","",IF(G42&lt;=20%,"Q1 Cheapest",IF(G42&lt;=40%,"Q2",IF(G42&lt;=60%,"Q3",IF(G42&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I42" s="16" t="n"/>
-      <c r="J42" s="16" t="n"/>
-      <c r="K42" s="16" t="n"/>
-      <c r="L42" s="16" t="n"/>
+      <c r="I42" s="30" t="n"/>
+      <c r="J42" s="30" t="n"/>
+      <c r="K42" s="30" t="n"/>
+      <c r="L42" s="30" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="n">
+      <c r="A43" s="31" t="n">
         <v>46112</v>
       </c>
-      <c r="B43" s="6" t="n">
+      <c r="B43" s="24" t="n">
         <v>29062.6</v>
       </c>
-      <c r="C43" s="7" t="n">
+      <c r="C43" s="25" t="n">
         <v>20.64</v>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -4135,15 +4153,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E43" s="21">
+      <c r="E43" s="33">
         <f>IFERROR(B43/C43,"")</f>
         <v/>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="30">
         <f>IF(AND(D43=D39,E39&lt;&gt;""),E43/E39-1,"")</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="30">
         <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4151,19 +4169,19 @@
         <f>IF(G43="","",IF(G43&lt;=20%,"Q1 Cheapest",IF(G43&lt;=40%,"Q2",IF(G43&lt;=60%,"Q3",IF(G43&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I43" s="16" t="n"/>
-      <c r="J43" s="16" t="n"/>
-      <c r="K43" s="16" t="n"/>
-      <c r="L43" s="16" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="30" t="n"/>
+      <c r="L43" s="30" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="n">
+      <c r="A44" s="31" t="n">
         <v>46203</v>
       </c>
-      <c r="B44" s="6" t="n">
+      <c r="B44" s="24" t="n">
         <v>26299.05</v>
       </c>
-      <c r="C44" s="7" t="n">
+      <c r="C44" s="25" t="n">
         <v>17.26</v>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -4171,15 +4189,15 @@
           <t>Consolidated</t>
         </is>
       </c>
-      <c r="E44" s="21">
+      <c r="E44" s="33">
         <f>IFERROR(B44/C44,"")</f>
         <v/>
       </c>
-      <c r="F44" s="16">
+      <c r="F44" s="30">
         <f>IF(AND(D44=D40,E40&lt;&gt;""),E44/E40-1,"")</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="30">
         <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
         <v/>
       </c>
@@ -4187,10 +4205,10 @@
         <f>IF(G44="","",IF(G44&lt;=20%,"Q1 Cheapest",IF(G44&lt;=40%,"Q2",IF(G44&lt;=60%,"Q3",IF(G44&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I44" s="16" t="n"/>
-      <c r="J44" s="16" t="n"/>
-      <c r="K44" s="16" t="n"/>
-      <c r="L44" s="16" t="n"/>
+      <c r="I44" s="30" t="n"/>
+      <c r="J44" s="30" t="n"/>
+      <c r="K44" s="30" t="n"/>
+      <c r="L44" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4267,30 +4285,30 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="n">
+      <c r="A2" s="31" t="n">
         <v>46283</v>
       </c>
-      <c r="B2" s="6" t="n">
+      <c r="B2" s="24" t="n">
         <v>28854.55</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="25" t="n">
         <v>18.41</v>
       </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="26" t="n">
         <v>0.0227272727273</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="26" t="n">
         <v>0.131881959322</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="34">
         <f>IF(D2="","",100*(1-D2))</f>
         <v/>
       </c>
-      <c r="G2" s="22">
+      <c r="G2" s="34">
         <f>IF(E2="","",IF(E2&lt;=0,20,IF(E2&lt;5%,20+400*E2,IF(E2&lt;10%,40+400*(E2-5%),IF(E2&lt;15%,60+400*(E2-10%),IF(E2&lt;25%,80+200*(E2-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H2" s="22">
+      <c r="H2" s="34">
         <f>IF(OR(F2="",G2=""),"",70%*F2+30%*G2)</f>
         <v/>
       </c>
@@ -4300,30 +4318,30 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="18" t="n">
+      <c r="A3" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="B3" s="6" t="n">
+      <c r="B3" s="24" t="n">
         <v>28830.9</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="25" t="n">
         <v>18.39</v>
       </c>
-      <c r="D3" s="8" t="n">
+      <c r="D3" s="26" t="n">
         <v>0.0227272727273</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="26" t="n">
         <v>0.131936196718</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="34">
         <f>IF(D3="","",100*(1-D3))</f>
         <v/>
       </c>
-      <c r="G3" s="22">
+      <c r="G3" s="34">
         <f>IF(E3="","",IF(E3&lt;=0,20,IF(E3&lt;5%,20+400*E3,IF(E3&lt;10%,40+400*(E3-5%),IF(E3&lt;15%,60+400*(E3-10%),IF(E3&lt;25%,80+200*(E3-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="34">
         <f>IF(OR(F3="",G3=""),"",70%*F3+30%*G3)</f>
         <v/>
       </c>
@@ -4333,30 +4351,30 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="n">
+      <c r="A4" s="31" t="n">
         <v>46287</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="24" t="n">
         <v>28582.1</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="25" t="n">
         <v>18.23</v>
       </c>
-      <c r="D4" s="8" t="n">
+      <c r="D4" s="26" t="n">
         <v>0.0227272727273</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="26" t="n">
         <v>0.132388104247</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="34">
         <f>IF(D4="","",100*(1-D4))</f>
         <v/>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="34">
         <f>IF(E4="","",IF(E4&lt;=0,20,IF(E4&lt;5%,20+400*E4,IF(E4&lt;10%,40+400*(E4-5%),IF(E4&lt;15%,60+400*(E4-10%),IF(E4&lt;25%,80+200*(E4-15%),100))))))</f>
         <v/>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="34">
         <f>IF(OR(F4="",G4=""),"",70%*F4+30%*G4)</f>
         <v/>
       </c>
@@ -4372,6 +4390,338 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="35" t="inlineStr">
+        <is>
+          <t>NIFTY IT Composition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>As of</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Weight coverage</t>
+        </is>
+      </c>
+      <c r="E2" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>NSE Indices — Indices Market Capitalisation &amp; Weightage</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Top 10 weight</t>
+        </is>
+      </c>
+      <c r="E3" s="26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="36" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="D5" s="36" t="inlineStr">
+        <is>
+          <t>Sector / Industry</t>
+        </is>
+      </c>
+      <c r="E5" s="36" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Infosys Ltd.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E6" s="37" t="n">
+        <v>0.2887</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services Ltd.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TCS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E7" s="37" t="n">
+        <v>0.2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>HCL Technologies Ltd.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>HCLTECH</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E8" s="37" t="n">
+        <v>0.1144</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tech Mahindra Ltd.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>0.1052</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Coforge Ltd.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E10" s="37" t="n">
+        <v>0.0703</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Persistent Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E11" s="37" t="n">
+        <v>0.0619</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wipro Ltd.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E12" s="37" t="n">
+        <v>0.0509</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LTM Ltd.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LTM</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E13" s="37" t="n">
+        <v>0.0429</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MphasiS Ltd.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E14" s="37" t="n">
+        <v>0.0327</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Oracle Financial Services Software Ltd.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E15" s="37" t="n">
+        <v>0.0304</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28582.1</v>
+        <v>28334.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.23</v>
+        <v>18.08</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1567.86066922655</v>
+        <v>1567.148783185841</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.132388104246566</v>
+        <v>0.1314880814568216</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05485463521667581</v>
+        <v>0.05530973451327434</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.95524169862639</v>
+        <v>72.59523258272863</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.29566341867883</v>
+        <v>90.1876606839095</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40513.51969281404</v>
+        <v>40495.12455752213</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.417443773998903</v>
+        <v>0.429203539823009</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.79623498830128</v>
+        <v>31.78720904546698</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49852.06626764267</v>
+        <v>49815.28597647753</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7441708715469706</v>
+        <v>0.7581420932227316</v>
       </c>
     </row>
     <row r="16">
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4380,6 +4380,39 @@
       </c>
       <c r="I4">
         <f>IF(H4="","",IF(H4&gt;=70,"BUY",IF(H4&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>28334.05</v>
+      </c>
+      <c r="C5" s="25" t="n">
+        <v>18.08</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.131488081457</v>
+      </c>
+      <c r="F5" s="34">
+        <f>IF(D5="","",100*(1-D5))</f>
+        <v/>
+      </c>
+      <c r="G5" s="34">
+        <f>IF(E5="","",IF(E5&lt;=0,20,IF(E5&lt;5%,20+400*E5,IF(E5&lt;10%,40+400*(E5-5%),IF(E5&lt;15%,60+400*(E5-10%),IF(E5&lt;25%,80+200*(E5-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H5" s="34">
+        <f>IF(OR(F5="",G5=""),"",70%*F5+30%*G5)</f>
+        <v/>
+      </c>
+      <c r="I5">
+        <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28334.05</v>
+        <v>28208.85</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.08</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1567.148783185841</v>
+        <v>1567.158333333333</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1314880814568216</v>
+        <v>0.1316742345766329</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05530973451327434</v>
+        <v>0.05555555555555555</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.59523258272863</v>
+        <v>72.66969383065315</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.1876606839095</v>
+        <v>90.20999905828685</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40495.12455752213</v>
+        <v>40495.37133333334</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.429203539823009</v>
+        <v>0.4355555555555557</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.78720904546698</v>
+        <v>31.78907589532566</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49815.28597647753</v>
+        <v>49818.5151983254</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7581420932227316</v>
+        <v>0.7660597719625368</v>
       </c>
     </row>
     <row r="16">
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4413,6 +4413,39 @@
       </c>
       <c r="I5">
         <f>IF(H5="","",IF(H5&gt;=70,"BUY",IF(H5&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="31" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>28208.85</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>18</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>0.131674234577</v>
+      </c>
+      <c r="F6" s="34">
+        <f>IF(D6="","",100*(1-D6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="34">
+        <f>IF(E6="","",IF(E6&lt;=0,20,IF(E6&lt;5%,20+400*E6,IF(E6&lt;10%,40+400*(E6-5%),IF(E6&lt;15%,60+400*(E6-10%),IF(E6&lt;25%,80+200*(E6-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H6" s="34">
+        <f>IF(OR(F6="",G6=""),"",70%*F6+30%*G6)</f>
+        <v/>
+      </c>
+      <c r="I6">
+        <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28208.85</v>
+        <v>28160.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18</v>
+        <v>17.96</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1567.158333333333</v>
+        <v>1567.978841870824</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1316742345766329</v>
+        <v>0.1323588166328604</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.05567928730512249</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.66969383065315</v>
+        <v>72.94352665314416</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.20999905828685</v>
+        <v>90.29214890503415</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40495.37133333334</v>
+        <v>40516.57327394209</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4355555555555557</v>
+        <v>0.4387527839643652</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.78907589532566</v>
+        <v>31.79594127537526</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49818.5151983254</v>
+        <v>49855.36317715563</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7660597719625368</v>
+        <v>0.770375349408422</v>
       </c>
     </row>
     <row r="16">
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4446,6 +4446,39 @@
       </c>
       <c r="I6">
         <f>IF(H6="","",IF(H6&gt;=70,"BUY",IF(H6&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="31" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>28160.9</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>17.96</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.132358816633</v>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(D7="","",100*(1-D7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>IF(E7="","",IF(E7&lt;=0,20,IF(E7&lt;5%,20+400*E7,IF(E7&lt;10%,40+400*(E7-5%),IF(E7&lt;15%,60+400*(E7-10%),IF(E7&lt;25%,80+200*(E7-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>IF(OR(F7="",G7=""),"",70%*F7+30%*G7)</f>
+        <v/>
+      </c>
+      <c r="I7">
+        <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28160.9</v>
+        <v>28086.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.96</v>
+        <v>17.92</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1567.978841870824</v>
+        <v>1567.327008928571</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1323588166328604</v>
+        <v>0.131942893517341</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05567928730512249</v>
+        <v>0.05580357142857142</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.94352665314416</v>
+        <v>72.7771574069364</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.29214890503415</v>
+        <v>90.24223813117183</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40516.57327394209</v>
+        <v>40499.72991071428</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4387527839643652</v>
+        <v>0.4419642857142854</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.79594127537526</v>
+        <v>31.79177016070248</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49855.36317715563</v>
+        <v>49828.10003451842</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.770375349408422</v>
+        <v>0.7740943170034864</v>
       </c>
     </row>
     <row r="16">
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4479,6 +4479,39 @@
       </c>
       <c r="I7">
         <f>IF(H7="","",IF(H7&gt;=70,"BUY",IF(H7&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>28086.5</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.131942893517</v>
+      </c>
+      <c r="F8" s="34">
+        <f>IF(D8="","",100*(1-D8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>IF(E8="","",IF(E8&lt;=0,20,IF(E8&lt;5%,20+400*E8,IF(E8&lt;10%,40+400*(E8-5%),IF(E8&lt;15%,60+400*(E8-10%),IF(E8&lt;25%,80+200*(E8-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>IF(OR(F8="",G8=""),"",70%*F8+30%*G8)</f>
+        <v/>
+      </c>
+      <c r="I8">
+        <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28086.5</v>
+        <v>27670</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.92</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1567.327008928571</v>
+        <v>1567.705382436261</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.131942893517341</v>
+        <v>0.1320516235447435</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05580357142857142</v>
+        <v>0.056657223796034</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.7771574069364</v>
+        <v>72.82064941789741</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.24223813117183</v>
+        <v>90.25528573446013</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -740,10 +740,10 @@
         <v>25.84</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40499.72991071428</v>
+        <v>40509.50708215298</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4419642857142854</v>
+        <v>0.4640226628895185</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.79177016070248</v>
+        <v>31.79286056754871</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49828.10003451842</v>
+        <v>49841.83863479167</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7740943170034864</v>
+        <v>0.8012952162917122</v>
       </c>
     </row>
     <row r="16">
@@ -4223,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4512,6 +4512,39 @@
       </c>
       <c r="I8">
         <f>IF(H8="","",IF(H8&gt;=70,"BUY",IF(H8&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="31" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>27670</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="D9" s="26" t="n">
+        <v>0.0227272727273</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.132051623545</v>
+      </c>
+      <c r="F9" s="34">
+        <f>IF(D9="","",100*(1-D9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="34">
+        <f>IF(E9="","",IF(E9&lt;=0,20,IF(E9&lt;5%,20+400*E9,IF(E9&lt;10%,40+400*(E9-5%),IF(E9&lt;15%,60+400*(E9-10%),IF(E9&lt;25%,80+200*(E9-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H9" s="34">
+        <f>IF(OR(F9="",G9=""),"",70%*F9+30%*G9)</f>
+        <v/>
+      </c>
+      <c r="I9">
+        <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -572,7 +572,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27670</v>
+        <v>27704.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.65</v>
+        <v>17.43</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.02985074626865672</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1567.705382436261</v>
+        <v>1589.489386115892</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1320516235447435</v>
+        <v>0.1471871184086517</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.056657223796034</v>
+        <v>0.05737234652897304</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.72727272727273</v>
+        <v>97.01492537313433</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>72.82064941789741</v>
+        <v>78.87484736346069</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.25528573446013</v>
+        <v>91.57290197023222</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.84</v>
+        <v>25.95481616835304</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>40509.50708215298</v>
+        <v>41254.9048181863</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4640226628895185</v>
+        <v>0.4890887073065426</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.79286056754871</v>
+        <v>31.94152339050832</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>49841.83863479167</v>
+        <v>50770.71240558548</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8012952162917122</v>
+        <v>0.832560148623541</v>
       </c>
     </row>
     <row r="16">
@@ -816,15 +816,17 @@
         <v>8</v>
       </c>
       <c r="C18" s="30" t="n">
-        <v>0.1780224341809005</v>
+        <v>0.1217876289155468</v>
       </c>
       <c r="D18" s="30" t="n">
-        <v>0.1460220480377938</v>
+        <v>0.1466221867591749</v>
       </c>
       <c r="E18" s="30" t="n">
         <v>0.2570055415900238</v>
       </c>
-      <c r="F18" s="30" t="n"/>
+      <c r="F18" s="30" t="n">
+        <v>0.1040894455060877</v>
+      </c>
       <c r="G18" s="30" t="n">
         <v>0</v>
       </c>
@@ -836,13 +838,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" s="30" t="n">
-        <v>0.2195443637358583</v>
+        <v>0.216022732816235</v>
       </c>
       <c r="D19" s="30" t="n">
-        <v>0.1081782378754973</v>
+        <v>0.09796119682890625</v>
       </c>
       <c r="E19" s="30" t="n">
         <v>0.210513148963401</v>
@@ -851,7 +853,7 @@
         <v>0.08989068682106849</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="20">
@@ -861,13 +863,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="30" t="n">
-        <v>0.09775659523541291</v>
+        <v>0.2491018299091641</v>
       </c>
       <c r="D20" s="30" t="n">
-        <v>0.1138441081150927</v>
+        <v>0.1094945852075572</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>0.179836325853753</v>
@@ -876,7 +878,7 @@
         <v>0.1142257588523116</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>0</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="21">
@@ -886,10 +888,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" s="30" t="n">
-        <v>0.1115554678272994</v>
+        <v>0.08393869933450149</v>
       </c>
       <c r="D21" s="30" t="n">
         <v>0.2228452356411557</v>
@@ -918,7 +920,7 @@
         <v>0.1517614731882273</v>
       </c>
       <c r="E22" s="30" t="n">
-        <v>0.1494827586704077</v>
+        <v>0.1298601869186647</v>
       </c>
       <c r="F22" s="30" t="n"/>
       <c r="G22" s="30" t="n">
@@ -939,7 +941,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -949,7 +951,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27">
@@ -972,7 +974,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2291,6 +2293,25 @@
       </c>
       <c r="E66" s="20">
         <f>IFERROR(1/C66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B67" s="24" t="n">
+        <v>27704.8</v>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="D67" s="32">
+        <f>IFERROR(B67/C67,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="20">
+        <f>IFERROR(1/C67,"")</f>
         <v/>
       </c>
     </row>
@@ -2307,7 +2328,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -2407,7 +2428,7 @@
       </c>
       <c r="F2" s="30" t="n"/>
       <c r="G2" s="30">
-        <f>IF(C2="","",(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,C2)+1)/2)/COUNTIFS($D$2:$D$44,D2,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C2="","",(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C2)+(COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,C2)+1)/2)/COUNTIFS($D$2:$D$45,D2,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H2">
@@ -2452,7 +2473,7 @@
       </c>
       <c r="F3" s="30" t="n"/>
       <c r="G3" s="30">
-        <f>IF(C3="","",(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,C3)+1)/2)/COUNTIFS($D$2:$D$44,D3,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C3="","",(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C3)+(COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,C3)+1)/2)/COUNTIFS($D$2:$D$45,D3,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H3">
@@ -2497,7 +2518,7 @@
       </c>
       <c r="F4" s="30" t="n"/>
       <c r="G4" s="30">
-        <f>IF(C4="","",(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,C4)+1)/2)/COUNTIFS($D$2:$D$44,D4,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C4="","",(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C4)+(COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,C4)+1)/2)/COUNTIFS($D$2:$D$45,D4,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H4">
@@ -2542,7 +2563,7 @@
       </c>
       <c r="F5" s="30" t="n"/>
       <c r="G5" s="30">
-        <f>IF(C5="","",(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,C5)+1)/2)/COUNTIFS($D$2:$D$44,D5,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C5="","",(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C5)+(COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,C5)+1)/2)/COUNTIFS($D$2:$D$45,D5,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H5">
@@ -2561,7 +2582,10 @@
         <f>IFERROR((B25/B5)^(1/5)-1,"")</f>
         <v/>
       </c>
-      <c r="L5" s="30" t="n"/>
+      <c r="L5" s="30">
+        <f>IFERROR((B45/B5)^(1/10)-1,"")</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="n">
@@ -2587,7 +2611,7 @@
         <v/>
       </c>
       <c r="G6" s="30">
-        <f>IF(C6="","",(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,C6)+1)/2)/COUNTIFS($D$2:$D$44,D6,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C6="","",(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C6)+(COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,C6)+1)/2)/COUNTIFS($D$2:$D$45,D6,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H6">
@@ -2632,7 +2656,7 @@
         <v/>
       </c>
       <c r="G7" s="30">
-        <f>IF(C7="","",(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,C7)+1)/2)/COUNTIFS($D$2:$D$44,D7,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C7="","",(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C7)+(COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,C7)+1)/2)/COUNTIFS($D$2:$D$45,D7,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H7">
@@ -2677,7 +2701,7 @@
         <v/>
       </c>
       <c r="G8" s="30">
-        <f>IF(C8="","",(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,C8)+1)/2)/COUNTIFS($D$2:$D$44,D8,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C8="","",(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C8)+(COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,C8)+1)/2)/COUNTIFS($D$2:$D$45,D8,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H8">
@@ -2722,7 +2746,7 @@
         <v/>
       </c>
       <c r="G9" s="30">
-        <f>IF(C9="","",(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,C9)+1)/2)/COUNTIFS($D$2:$D$44,D9,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C9="","",(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C9)+(COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,C9)+1)/2)/COUNTIFS($D$2:$D$45,D9,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H9">
@@ -2767,7 +2791,7 @@
         <v/>
       </c>
       <c r="G10" s="30">
-        <f>IF(C10="","",(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,C10)+1)/2)/COUNTIFS($D$2:$D$44,D10,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C10="","",(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C10)+(COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,C10)+1)/2)/COUNTIFS($D$2:$D$45,D10,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H10">
@@ -2812,7 +2836,7 @@
         <v/>
       </c>
       <c r="G11" s="30">
-        <f>IF(C11="","",(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,C11)+1)/2)/COUNTIFS($D$2:$D$44,D11,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C11="","",(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C11)+(COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,C11)+1)/2)/COUNTIFS($D$2:$D$45,D11,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H11">
@@ -2857,7 +2881,7 @@
         <v/>
       </c>
       <c r="G12" s="30">
-        <f>IF(C12="","",(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,C12)+1)/2)/COUNTIFS($D$2:$D$44,D12,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C12="","",(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C12)+(COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,C12)+1)/2)/COUNTIFS($D$2:$D$45,D12,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H12">
@@ -2902,7 +2926,7 @@
         <v/>
       </c>
       <c r="G13" s="30">
-        <f>IF(C13="","",(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,C13)+1)/2)/COUNTIFS($D$2:$D$44,D13,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C13="","",(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C13)+(COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,C13)+1)/2)/COUNTIFS($D$2:$D$45,D13,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H13">
@@ -2947,7 +2971,7 @@
         <v/>
       </c>
       <c r="G14" s="30">
-        <f>IF(C14="","",(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,C14)+1)/2)/COUNTIFS($D$2:$D$44,D14,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C14="","",(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C14)+(COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,C14)+1)/2)/COUNTIFS($D$2:$D$45,D14,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H14">
@@ -2992,7 +3016,7 @@
         <v/>
       </c>
       <c r="G15" s="30">
-        <f>IF(C15="","",(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,C15)+1)/2)/COUNTIFS($D$2:$D$44,D15,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C15="","",(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C15)+(COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,C15)+1)/2)/COUNTIFS($D$2:$D$45,D15,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H15">
@@ -3037,7 +3061,7 @@
         <v/>
       </c>
       <c r="G16" s="30">
-        <f>IF(C16="","",(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,C16)+1)/2)/COUNTIFS($D$2:$D$44,D16,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C16="","",(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C16)+(COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,C16)+1)/2)/COUNTIFS($D$2:$D$45,D16,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H16">
@@ -3082,7 +3106,7 @@
         <v/>
       </c>
       <c r="G17" s="30">
-        <f>IF(C17="","",(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,C17)+1)/2)/COUNTIFS($D$2:$D$44,D17,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C17="","",(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C17)+(COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,C17)+1)/2)/COUNTIFS($D$2:$D$45,D17,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H17">
@@ -3127,7 +3151,7 @@
         <v/>
       </c>
       <c r="G18" s="30">
-        <f>IF(C18="","",(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,C18)+1)/2)/COUNTIFS($D$2:$D$44,D18,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C18="","",(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C18)+(COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,C18)+1)/2)/COUNTIFS($D$2:$D$45,D18,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H18">
@@ -3172,7 +3196,7 @@
         <v/>
       </c>
       <c r="G19" s="30">
-        <f>IF(C19="","",(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,C19)+1)/2)/COUNTIFS($D$2:$D$44,D19,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C19="","",(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C19)+(COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,C19)+1)/2)/COUNTIFS($D$2:$D$45,D19,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H19">
@@ -3217,7 +3241,7 @@
         <v/>
       </c>
       <c r="G20" s="30">
-        <f>IF(C20="","",(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,C20)+1)/2)/COUNTIFS($D$2:$D$44,D20,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C20="","",(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C20)+(COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,C20)+1)/2)/COUNTIFS($D$2:$D$45,D20,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H20">
@@ -3262,7 +3286,7 @@
         <v/>
       </c>
       <c r="G21" s="30">
-        <f>IF(C21="","",(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,C21)+1)/2)/COUNTIFS($D$2:$D$44,D21,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C21="","",(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C21)+(COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,C21)+1)/2)/COUNTIFS($D$2:$D$45,D21,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H21">
@@ -3307,7 +3331,7 @@
         <v/>
       </c>
       <c r="G22" s="30">
-        <f>IF(C22="","",(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,C22)+1)/2)/COUNTIFS($D$2:$D$44,D22,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C22="","",(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C22)+(COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,C22)+1)/2)/COUNTIFS($D$2:$D$45,D22,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H22">
@@ -3352,7 +3376,7 @@
         <v/>
       </c>
       <c r="G23" s="30">
-        <f>IF(C23="","",(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,C23)+1)/2)/COUNTIFS($D$2:$D$44,D23,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C23="","",(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C23)+(COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,C23)+1)/2)/COUNTIFS($D$2:$D$45,D23,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H23">
@@ -3397,7 +3421,7 @@
         <v/>
       </c>
       <c r="G24" s="30">
-        <f>IF(C24="","",(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,C24)+1)/2)/COUNTIFS($D$2:$D$44,D24,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C24="","",(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C24)+(COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,C24)+1)/2)/COUNTIFS($D$2:$D$45,D24,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H24">
@@ -3442,7 +3466,7 @@
         <v/>
       </c>
       <c r="G25" s="30">
-        <f>IF(C25="","",(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,C25)+1)/2)/COUNTIFS($D$2:$D$44,D25,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C25="","",(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C25)+(COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,C25)+1)/2)/COUNTIFS($D$2:$D$45,D25,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H25">
@@ -3457,7 +3481,10 @@
         <f>IFERROR((B37/B25)^(1/3)-1,"")</f>
         <v/>
       </c>
-      <c r="K25" s="30" t="n"/>
+      <c r="K25" s="30">
+        <f>IFERROR((B45/B25)^(1/5)-1,"")</f>
+        <v/>
+      </c>
       <c r="L25" s="30" t="n"/>
     </row>
     <row r="26">
@@ -3484,7 +3511,7 @@
         <v/>
       </c>
       <c r="G26" s="30">
-        <f>IF(C26="","",(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,C26)+1)/2)/COUNTIFS($D$2:$D$44,D26,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C26="","",(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C26)+(COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,C26)+1)/2)/COUNTIFS($D$2:$D$45,D26,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H26">
@@ -3526,7 +3553,7 @@
         <v/>
       </c>
       <c r="G27" s="30">
-        <f>IF(C27="","",(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,C27)+1)/2)/COUNTIFS($D$2:$D$44,D27,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C27="","",(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C27)+(COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,C27)+1)/2)/COUNTIFS($D$2:$D$45,D27,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H27">
@@ -3568,7 +3595,7 @@
         <v/>
       </c>
       <c r="G28" s="30">
-        <f>IF(C28="","",(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,C28)+1)/2)/COUNTIFS($D$2:$D$44,D28,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C28="","",(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C28)+(COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,C28)+1)/2)/COUNTIFS($D$2:$D$45,D28,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H28">
@@ -3610,7 +3637,7 @@
         <v/>
       </c>
       <c r="G29" s="30">
-        <f>IF(C29="","",(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,C29)+1)/2)/COUNTIFS($D$2:$D$44,D29,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C29="","",(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C29)+(COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,C29)+1)/2)/COUNTIFS($D$2:$D$45,D29,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H29">
@@ -3652,7 +3679,7 @@
         <v/>
       </c>
       <c r="G30" s="30">
-        <f>IF(C30="","",(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,C30)+1)/2)/COUNTIFS($D$2:$D$44,D30,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C30="","",(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C30)+(COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,C30)+1)/2)/COUNTIFS($D$2:$D$45,D30,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H30">
@@ -3694,7 +3721,7 @@
         <v/>
       </c>
       <c r="G31" s="30">
-        <f>IF(C31="","",(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,C31)+1)/2)/COUNTIFS($D$2:$D$44,D31,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C31="","",(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C31)+(COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,C31)+1)/2)/COUNTIFS($D$2:$D$45,D31,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H31">
@@ -3736,7 +3763,7 @@
         <v/>
       </c>
       <c r="G32" s="30">
-        <f>IF(C32="","",(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,C32)+1)/2)/COUNTIFS($D$2:$D$44,D32,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C32="","",(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C32)+(COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,C32)+1)/2)/COUNTIFS($D$2:$D$45,D32,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H32">
@@ -3778,7 +3805,7 @@
         <v/>
       </c>
       <c r="G33" s="30">
-        <f>IF(C33="","",(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,C33)+1)/2)/COUNTIFS($D$2:$D$44,D33,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C33="","",(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C33)+(COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,C33)+1)/2)/COUNTIFS($D$2:$D$45,D33,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H33">
@@ -3789,7 +3816,10 @@
         <f>IFERROR(B37/B33-1,"")</f>
         <v/>
       </c>
-      <c r="J33" s="30" t="n"/>
+      <c r="J33" s="30">
+        <f>IFERROR((B45/B33)^(1/3)-1,"")</f>
+        <v/>
+      </c>
       <c r="K33" s="30" t="n"/>
       <c r="L33" s="30" t="n"/>
     </row>
@@ -3817,7 +3847,7 @@
         <v/>
       </c>
       <c r="G34" s="30">
-        <f>IF(C34="","",(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,C34)+1)/2)/COUNTIFS($D$2:$D$44,D34,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C34="","",(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C34)+(COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,C34)+1)/2)/COUNTIFS($D$2:$D$45,D34,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H34">
@@ -3856,7 +3886,7 @@
         <v/>
       </c>
       <c r="G35" s="30">
-        <f>IF(C35="","",(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,C35)+1)/2)/COUNTIFS($D$2:$D$44,D35,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C35="","",(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C35)+(COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,C35)+1)/2)/COUNTIFS($D$2:$D$45,D35,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H35">
@@ -3895,7 +3925,7 @@
         <v/>
       </c>
       <c r="G36" s="30">
-        <f>IF(C36="","",(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,C36)+1)/2)/COUNTIFS($D$2:$D$44,D36,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C36="","",(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C36)+(COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,C36)+1)/2)/COUNTIFS($D$2:$D$45,D36,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H36">
@@ -3934,7 +3964,7 @@
         <v/>
       </c>
       <c r="G37" s="30">
-        <f>IF(C37="","",(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,C37)+1)/2)/COUNTIFS($D$2:$D$44,D37,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C37="","",(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C37)+(COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,C37)+1)/2)/COUNTIFS($D$2:$D$45,D37,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H37">
@@ -3973,7 +4003,7 @@
         <v/>
       </c>
       <c r="G38" s="30">
-        <f>IF(C38="","",(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,C38)+1)/2)/COUNTIFS($D$2:$D$44,D38,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C38="","",(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C38)+(COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,C38)+1)/2)/COUNTIFS($D$2:$D$45,D38,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H38">
@@ -4012,7 +4042,7 @@
         <v/>
       </c>
       <c r="G39" s="30">
-        <f>IF(C39="","",(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,C39)+1)/2)/COUNTIFS($D$2:$D$44,D39,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C39="","",(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C39)+(COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,C39)+1)/2)/COUNTIFS($D$2:$D$45,D39,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H39">
@@ -4051,7 +4081,7 @@
         <v/>
       </c>
       <c r="G40" s="30">
-        <f>IF(C40="","",(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,C40)+1)/2)/COUNTIFS($D$2:$D$44,D40,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C40="","",(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C40)+(COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,C40)+1)/2)/COUNTIFS($D$2:$D$45,D40,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H40">
@@ -4090,14 +4120,17 @@
         <v/>
       </c>
       <c r="G41" s="30">
-        <f>IF(C41="","",(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,C41)+1)/2)/COUNTIFS($D$2:$D$44,D41,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C41="","",(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C41)+(COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,C41)+1)/2)/COUNTIFS($D$2:$D$45,D41,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H41">
         <f>IF(G41="","",IF(G41&lt;=20%,"Q1 Cheapest",IF(G41&lt;=40%,"Q2",IF(G41&lt;=60%,"Q3",IF(G41&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
         <v/>
       </c>
-      <c r="I41" s="30" t="n"/>
+      <c r="I41" s="30">
+        <f>IFERROR(B45/B41-1,"")</f>
+        <v/>
+      </c>
       <c r="J41" s="30" t="n"/>
       <c r="K41" s="30" t="n"/>
       <c r="L41" s="30" t="n"/>
@@ -4126,7 +4159,7 @@
         <v/>
       </c>
       <c r="G42" s="30">
-        <f>IF(C42="","",(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,C42)+1)/2)/COUNTIFS($D$2:$D$44,D42,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C42="","",(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C42)+(COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,C42)+1)/2)/COUNTIFS($D$2:$D$45,D42,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H42">
@@ -4162,7 +4195,7 @@
         <v/>
       </c>
       <c r="G43" s="30">
-        <f>IF(C43="","",(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,C43)+1)/2)/COUNTIFS($D$2:$D$44,D43,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C43="","",(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C43)+(COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,C43)+1)/2)/COUNTIFS($D$2:$D$45,D43,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H43">
@@ -4198,7 +4231,7 @@
         <v/>
       </c>
       <c r="G44" s="30">
-        <f>IF(C44="","",(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0",$C$2:$C$44,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,C44)+1)/2)/COUNTIFS($D$2:$D$44,D44,$C$2:$C$44,"&gt;0"))</f>
+        <f>IF(C44="","",(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C44)+(COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,C44)+1)/2)/COUNTIFS($D$2:$D$45,D44,$C$2:$C$45,"&gt;0"))</f>
         <v/>
       </c>
       <c r="H44">
@@ -4209,6 +4242,42 @@
       <c r="J44" s="30" t="n"/>
       <c r="K44" s="30" t="n"/>
       <c r="L44" s="30" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B45" s="24" t="n">
+        <v>27704.8</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Consolidated</t>
+        </is>
+      </c>
+      <c r="E45" s="33">
+        <f>IFERROR(B45/C45,"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="30">
+        <f>IF(AND(D45=D41,E41&lt;&gt;""),E45/E41-1,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="30">
+        <f>IF(C45="","",(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0",$C$2:$C$45,"&lt;"&amp;C45)+(COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,C45)+1)/2)/COUNTIFS($D$2:$D$45,D45,$C$2:$C$45,"&gt;0"))</f>
+        <v/>
+      </c>
+      <c r="H45">
+        <f>IF(G45="","",IF(G45&lt;=20%,"Q1 Cheapest",IF(G45&lt;=40%,"Q2",IF(G45&lt;=60%,"Q3",IF(G45&lt;=80%,"Q4","Q5 Most Expensive")))))</f>
+        <v/>
+      </c>
+      <c r="I45" s="30" t="n"/>
+      <c r="J45" s="30" t="n"/>
+      <c r="K45" s="30" t="n"/>
+      <c r="L45" s="30" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -4223,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4231,7 +4300,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
@@ -4545,6 +4614,39 @@
       </c>
       <c r="I9">
         <f>IF(H9="","",IF(H9&gt;=70,"BUY",IF(H9&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="31" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>27704.8</v>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>0.0298507462687</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>0.147187118409</v>
+      </c>
+      <c r="F10" s="34">
+        <f>IF(D10="","",100*(1-D10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="34">
+        <f>IF(E10="","",IF(E10&lt;=0,20,IF(E10&lt;5%,20+400*E10,IF(E10&lt;10%,40+400*(E10-5%),IF(E10&lt;15%,60+400*(E10-10%),IF(E10&lt;25%,80+200*(E10-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H10" s="34">
+        <f>IF(OR(F10="",G10=""),"",70%*F10+30%*G10)</f>
+        <v/>
+      </c>
+      <c r="I10">
+        <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -4585,7 +4687,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -4665,7 +4767,7 @@
         </is>
       </c>
       <c r="E6" s="37" t="n">
-        <v>0.2887</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="7">
@@ -4688,7 +4790,7 @@
         </is>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.2026</v>
+        <v>0.1908</v>
       </c>
     </row>
     <row r="8">
@@ -4711,7 +4813,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>0.1144</v>
+        <v>0.1181</v>
       </c>
     </row>
     <row r="9">
@@ -4734,7 +4836,7 @@
         </is>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.1052</v>
+        <v>0.1047</v>
       </c>
     </row>
     <row r="10">
@@ -4757,7 +4859,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>0.0703</v>
+        <v>0.0659</v>
       </c>
     </row>
     <row r="11">
@@ -4780,7 +4882,7 @@
         </is>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.0619</v>
+        <v>0.0621</v>
       </c>
     </row>
     <row r="12">
@@ -4803,7 +4905,7 @@
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>0.0509</v>
+        <v>0.0464</v>
       </c>
     </row>
     <row r="13">
@@ -4826,7 +4928,7 @@
         </is>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0.0429</v>
+        <v>0.0406</v>
       </c>
     </row>
     <row r="14">
@@ -4849,7 +4951,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>0.0327</v>
+        <v>0.0309</v>
       </c>
     </row>
     <row r="15">
@@ -4872,7 +4974,7 @@
         </is>
       </c>
       <c r="E15" s="37" t="n">
-        <v>0.0304</v>
+        <v>0.0275</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27704.8</v>
+        <v>28304.7</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.43</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.02985074626865672</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1589.489386115892</v>
+        <v>1590.151685393259</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1471871184086517</v>
+        <v>0.1476414161123674</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05737234652897304</v>
+        <v>0.05617977528089887</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>97.01492537313433</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>78.87484736346069</v>
+        <v>79.05656644494694</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.57290197023222</v>
+        <v>91.10502963497662</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.95481616835304</v>
+        <v>25.97383436822402</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41254.9048181863</v>
+        <v>41302.33649675676</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4890887073065426</v>
+        <v>0.4592041779901133</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.94152339050832</v>
+        <v>31.94769145533134</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50770.71240558548</v>
+        <v>50801.67541211894</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.832560148623541</v>
+        <v>0.7948141267040081</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4647,6 +4647,39 @@
       </c>
       <c r="I10">
         <f>IF(H10="","",IF(H10&gt;=70,"BUY",IF(H10&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B11" s="24" t="n">
+        <v>28304.7</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>0.147641416112</v>
+      </c>
+      <c r="F11" s="34">
+        <f>IF(D11="","",100*(1-D11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="34">
+        <f>IF(E11="","",IF(E11&lt;=0,20,IF(E11&lt;5%,20+400*E11,IF(E11&lt;10%,40+400*(E11-5%),IF(E11&lt;15%,60+400*(E11-10%),IF(E11&lt;25%,80+200*(E11-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H11" s="34">
+        <f>IF(OR(F11="",G11=""),"",70%*F11+30%*G11)</f>
+        <v/>
+      </c>
+      <c r="I11">
+        <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28304.7</v>
+        <v>28301.65</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1590.151685393259</v>
+        <v>1589.980337078652</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1476414161123674</v>
+        <v>0.1478852734349372</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>79.05656644494694</v>
+        <v>79.15410937397488</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.10502963497662</v>
+        <v>91.134292513685</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.97383436822402</v>
+        <v>25.984042932482</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41302.33649675676</v>
+        <v>41314.11734045389</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4592041779901133</v>
+        <v>0.4597776928360673</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.94769145533134</v>
+        <v>31.95100234103663</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50801.67541211894</v>
+        <v>50801.46547220222</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7948141267040081</v>
+        <v>0.7950001315189119</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4680,6 +4680,39 @@
       </c>
       <c r="I11">
         <f>IF(H11="","",IF(H11&gt;=70,"BUY",IF(H11&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="31" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B12" s="24" t="n">
+        <v>28301.65</v>
+      </c>
+      <c r="C12" s="25" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>0.147885273435</v>
+      </c>
+      <c r="F12" s="34">
+        <f>IF(D12="","",100*(1-D12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="34">
+        <f>IF(E12="","",IF(E12&lt;=0,20,IF(E12&lt;5%,20+400*E12,IF(E12&lt;10%,40+400*(E12-5%),IF(E12&lt;15%,60+400*(E12-10%),IF(E12&lt;25%,80+200*(E12-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H12" s="34">
+        <f>IF(OR(F12="",G12=""),"",70%*F12+30%*G12)</f>
+        <v/>
+      </c>
+      <c r="I12">
+        <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28301.65</v>
+        <v>28136.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1589.980337078652</v>
+        <v>1589.607344632768</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1478852734349372</v>
+        <v>0.1472549515875059</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05617977528089887</v>
+        <v>0.05649717514124294</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>79.15410937397488</v>
+        <v>78.90198063500236</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.134292513685</v>
+        <v>91.05865389199325</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.984042932482</v>
+        <v>25.95765585902896</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41314.11734045389</v>
+        <v>41262.48040296225</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4597776928360673</v>
+        <v>0.4665342293236701</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.95100234103663</v>
+        <v>31.94244437126808</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50801.46547220222</v>
+        <v>50775.94417809138</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7950001315189119</v>
+        <v>0.8046578740829426</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4713,6 +4713,39 @@
       </c>
       <c r="I12">
         <f>IF(H12="","",IF(H12&gt;=70,"BUY",IF(H12&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="31" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B13" s="24" t="n">
+        <v>28136.05</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>0.147254951588</v>
+      </c>
+      <c r="F13" s="34">
+        <f>IF(D13="","",100*(1-D13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="34">
+        <f>IF(E13="","",IF(E13&lt;=0,20,IF(E13&lt;5%,20+400*E13,IF(E13&lt;10%,40+400*(E13-5%),IF(E13&lt;15%,60+400*(E13-10%),IF(E13&lt;25%,80+200*(E13-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H13" s="34">
+        <f>IF(OR(F13="",G13=""),"",70%*F13+30%*G13)</f>
+        <v/>
+      </c>
+      <c r="I13">
+        <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28136.05</v>
+        <v>27757.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.7</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1589.607344632768</v>
+        <v>1589.79381443299</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1472549515875059</v>
+        <v>0.1473628954519992</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05649717514124294</v>
+        <v>0.0572737686139748</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>78.90198063500236</v>
+        <v>78.94515818079968</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.05865389199325</v>
+        <v>91.07160715573244</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.95765585902896</v>
+        <v>25.96217469760769</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41262.48040296225</v>
+        <v>41274.50474348537</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4665342293236701</v>
+        <v>0.4869515863463736</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.94244437126808</v>
+        <v>31.94390994053686</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50775.94417809138</v>
+        <v>50784.23043226998</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8046578740829426</v>
+        <v>0.8295481065599573</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4746,6 +4746,39 @@
       </c>
       <c r="I13">
         <f>IF(H13="","",IF(H13&gt;=70,"BUY",IF(H13&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="31" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B14" s="24" t="n">
+        <v>27757.8</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.147362895452</v>
+      </c>
+      <c r="F14" s="34">
+        <f>IF(D14="","",100*(1-D14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="34">
+        <f>IF(E14="","",IF(E14&lt;=0,20,IF(E14&lt;5%,20+400*E14,IF(E14&lt;10%,40+400*(E14-5%),IF(E14&lt;15%,60+400*(E14-10%),IF(E14&lt;25%,80+200*(E14-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H14" s="34">
+        <f>IF(OR(F14="",G14=""),"",70%*F14+30%*G14)</f>
+        <v/>
+      </c>
+      <c r="I14">
+        <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27757.8</v>
+        <v>27736.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.46</v>
+        <v>17.45</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1589.79381443299</v>
+        <v>1589.489971346705</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1473628954519992</v>
+        <v>0.1472667040760074</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.0572737686139748</v>
+        <v>0.05730659025787966</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>78.94515818079968</v>
+        <v>78.90668163040296</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.07160715573244</v>
+        <v>91.06006419061342</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.96217469760769</v>
+        <v>25.95814785177617</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41274.50474348537</v>
+        <v>41260.21568513323</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4869515863463736</v>
+        <v>0.487572942795196</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.94390994053686</v>
+        <v>31.94260393648339</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50784.23043226998</v>
+        <v>50772.44861574013</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8295481065599573</v>
+        <v>0.8305217155577875</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4779,6 +4779,39 @@
       </c>
       <c r="I14">
         <f>IF(H14="","",IF(H14&gt;=70,"BUY",IF(H14&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="31" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B15" s="24" t="n">
+        <v>27736.6</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>17.45</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.147266704076</v>
+      </c>
+      <c r="F15" s="34">
+        <f>IF(D15="","",100*(1-D15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="34">
+        <f>IF(E15="","",IF(E15&lt;=0,20,IF(E15&lt;5%,20+400*E15,IF(E15&lt;10%,40+400*(E15-5%),IF(E15&lt;15%,60+400*(E15-10%),IF(E15&lt;25%,80+200*(E15-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H15" s="34">
+        <f>IF(OR(F15="",G15=""),"",70%*F15+30%*G15)</f>
+        <v/>
+      </c>
+      <c r="I15">
+        <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>27736.6</v>
+        <v>28574.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.45</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1589.489971346705</v>
+        <v>1590.14468558709</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1472667040760074</v>
+        <v>0.1479158907419607</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05730659025787966</v>
+        <v>0.05564830272676684</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>78.90668163040296</v>
+        <v>79.16635629678426</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.06006419061342</v>
+        <v>91.13796659052781</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.95814785177617</v>
+        <v>25.98532466043202</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41260.21568513323</v>
+        <v>41320.42591204112</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.487572942795196</v>
+        <v>0.4460392131570403</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.94260393648339</v>
+        <v>31.95141803658799</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50772.44861574013</v>
+        <v>50807.37758785187</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8305217155577875</v>
+        <v>0.7780421834495264</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4812,6 +4812,39 @@
       </c>
       <c r="I15">
         <f>IF(H15="","",IF(H15&gt;=70,"BUY",IF(H15&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="31" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B16" s="24" t="n">
+        <v>28574.9</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>17.97</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>0.147915890742</v>
+      </c>
+      <c r="F16" s="34">
+        <f>IF(D16="","",100*(1-D16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="34">
+        <f>IF(E16="","",IF(E16&lt;=0,20,IF(E16&lt;5%,20+400*E16,IF(E16&lt;10%,40+400*(E16-5%),IF(E16&lt;15%,60+400*(E16-10%),IF(E16&lt;25%,80+200*(E16-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H16" s="34">
+        <f>IF(OR(F16="",G16=""),"",70%*F16+30%*G16)</f>
+        <v/>
+      </c>
+      <c r="I16">
+        <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28574.9</v>
+        <v>28349.6</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.97</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1590.14468558709</v>
+        <v>1602.577727529678</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1479158907419607</v>
+        <v>0.155722942425089</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05564830272676684</v>
+        <v>0.05652911249293386</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>79.16635629678426</v>
+        <v>81.14458848501781</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.13796659052781</v>
+        <v>91.73143624699787</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>25.98532466043202</v>
+        <v>26.19236078916057</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41320.42591204112</v>
+        <v>41975.29403213038</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4460392131570403</v>
+        <v>0.4806309095059678</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.95141803658799</v>
+        <v>32.05427100058436</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>50807.37758785187</v>
+        <v>51369.46077773692</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7780421834495264</v>
+        <v>0.8119994912710207</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4845,6 +4845,39 @@
       </c>
       <c r="I16">
         <f>IF(H16="","",IF(H16&gt;=70,"BUY",IF(H16&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <v>28349.6</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>0.155722942425</v>
+      </c>
+      <c r="F17" s="34">
+        <f>IF(D17="","",100*(1-D17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="34">
+        <f>IF(E17="","",IF(E17&lt;=0,20,IF(E17&lt;5%,20+400*E17,IF(E17&lt;10%,40+400*(E17-5%),IF(E17&lt;15%,60+400*(E17-10%),IF(E17&lt;25%,80+200*(E17-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H17" s="34">
+        <f>IF(OR(F17="",G17=""),"",70%*F17+30%*G17)</f>
+        <v/>
+      </c>
+      <c r="I17">
+        <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>28349.6</v>
+        <v>29830.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>17.69</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1602.577727529678</v>
+        <v>1611.566720691518</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.155722942425089</v>
+        <v>0.1622357841662196</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05652911249293386</v>
+        <v>0.05402485143165856</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>81.14458848501781</v>
+        <v>82.44715683324392</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.73143624699787</v>
+        <v>92.12220675146571</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.19236078916057</v>
+        <v>26.23245370529823</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>41975.29403213038</v>
+        <v>42275.34939353953</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4806309095059678</v>
+        <v>0.417204414116598</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.05427100058436</v>
+        <v>32.15375000615031</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51369.46077773692</v>
+        <v>51817.91345534653</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.8119994912710207</v>
+        <v>0.737101567052961</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4878,6 +4878,39 @@
       </c>
       <c r="I17">
         <f>IF(H17="","",IF(H17&gt;=70,"BUY",IF(H17&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="31" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B18" s="24" t="n">
+        <v>29830.1</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0.162235784166</v>
+      </c>
+      <c r="F18" s="34">
+        <f>IF(D18="","",100*(1-D18))</f>
+        <v/>
+      </c>
+      <c r="G18" s="34">
+        <f>IF(E18="","",IF(E18&lt;=0,20,IF(E18&lt;5%,20+400*E18,IF(E18&lt;10%,40+400*(E18-5%),IF(E18&lt;15%,60+400*(E18-10%),IF(E18&lt;25%,80+200*(E18-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H18" s="34">
+        <f>IF(OR(F18="",G18=""),"",70%*F18+30%*G18)</f>
+        <v/>
+      </c>
+      <c r="I18">
+        <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>29830.1</v>
+        <v>30171</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.51</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1611.566720691518</v>
+        <v>1611.698717948718</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1622357841662196</v>
+        <v>0.1624967147637271</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05402485143165856</v>
+        <v>0.05341880341880342</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.44715683324392</v>
+        <v>82.49934295274541</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.12220675146571</v>
+        <v>92.13786258731616</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.23245370529823</v>
+        <v>26.23348699046436</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42275.34939353953</v>
+        <v>42280.47734985578</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.417204414116598</v>
+        <v>0.4013614845333524</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.15375000615031</v>
+        <v>32.15773553464824</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51817.91345534653</v>
+        <v>51828.5811333265</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.737101567052961</v>
+        <v>0.7178277529192436</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4911,6 +4911,39 @@
       </c>
       <c r="I18">
         <f>IF(H18="","",IF(H18&gt;=70,"BUY",IF(H18&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="31" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B19" s="24" t="n">
+        <v>30171</v>
+      </c>
+      <c r="C19" s="25" t="n">
+        <v>18.72</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>0.162496714764</v>
+      </c>
+      <c r="F19" s="34">
+        <f>IF(D19="","",100*(1-D19))</f>
+        <v/>
+      </c>
+      <c r="G19" s="34">
+        <f>IF(E19="","",IF(E19&lt;=0,20,IF(E19&lt;5%,20+400*E19,IF(E19&lt;10%,40+400*(E19-5%),IF(E19&lt;15%,60+400*(E19-10%),IF(E19&lt;25%,80+200*(E19-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H19" s="34">
+        <f>IF(OR(F19="",G19=""),"",70%*F19+30%*G19)</f>
+        <v/>
+      </c>
+      <c r="I19">
+        <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30171</v>
+        <v>30719.8</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>18.72</v>
+        <v>19.06</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1611.698717948718</v>
+        <v>1611.741867785939</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1624967147637271</v>
+        <v>0.1604861958957902</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05341880341880342</v>
+        <v>0.05246589716684156</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.49934295274541</v>
+        <v>82.09723917915804</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.13786258731616</v>
+        <v>92.01723145523995</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.23348699046436</v>
+        <v>26.22552533574733</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42280.47734985578</v>
+        <v>42268.77718830487</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.4013614845333524</v>
+        <v>0.3759457154117172</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.15773553464824</v>
+        <v>32.12702629502541</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51828.5811333265</v>
+        <v>51780.47336715223</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.7178277529192436</v>
+        <v>0.6855732578712177</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4944,6 +4944,39 @@
       </c>
       <c r="I19">
         <f>IF(H19="","",IF(H19&gt;=70,"BUY",IF(H19&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B20" s="24" t="n">
+        <v>30719.8</v>
+      </c>
+      <c r="C20" s="25" t="n">
+        <v>19.06</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0.160486195896</v>
+      </c>
+      <c r="F20" s="34">
+        <f>IF(D20="","",100*(1-D20))</f>
+        <v/>
+      </c>
+      <c r="G20" s="34">
+        <f>IF(E20="","",IF(E20&lt;=0,20,IF(E20&lt;5%,20+400*E20,IF(E20&lt;10%,40+400*(E20-5%),IF(E20&lt;15%,60+400*(E20-10%),IF(E20&lt;25%,80+200*(E20-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H20" s="34">
+        <f>IF(OR(F20="",G20=""),"",70%*F20+30%*G20)</f>
+        <v/>
+      </c>
+      <c r="I20">
+        <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>30719.8</v>
+        <v>31924.1</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.06</v>
+        <v>19.75</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1611.741867785939</v>
+        <v>1616.410126582279</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1604861958957902</v>
+        <v>0.1637081098919024</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05246589716684156</v>
+        <v>0.05063291139240506</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.09723917915804</v>
+        <v>82.74162197838049</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>92.01723145523995</v>
+        <v>91.1657701756037</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.22552533574733</v>
+        <v>26.23828411517193</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42268.77718830487</v>
+        <v>42411.82814790685</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3759457154117172</v>
+        <v>0.32852071469225</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.12702629502541</v>
+        <v>32.17623872994889</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51780.47336715223</v>
+        <v>52009.99811841829</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6855732578712177</v>
+        <v>0.6291766445543741</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -4977,6 +4977,39 @@
       </c>
       <c r="I20">
         <f>IF(H20="","",IF(H20&gt;=70,"BUY",IF(H20&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B21" s="24" t="n">
+        <v>31924.1</v>
+      </c>
+      <c r="C21" s="25" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0.163708109892</v>
+      </c>
+      <c r="F21" s="34">
+        <f>IF(D21="","",100*(1-D21))</f>
+        <v/>
+      </c>
+      <c r="G21" s="34">
+        <f>IF(E21="","",IF(E21&lt;=0,20,IF(E21&lt;5%,20+400*E21,IF(E21&lt;10%,40+400*(E21-5%),IF(E21&lt;15%,60+400*(E21-10%),IF(E21&lt;25%,80+200*(E21-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H21" s="34">
+        <f>IF(OR(F21="",G21=""),"",70%*F21+30%*G21)</f>
+        <v/>
+      </c>
+      <c r="I21">
+        <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31924.1</v>
+        <v>31516.3</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.75</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1616.410126582279</v>
+        <v>1616.220512820513</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1637081098919024</v>
+        <v>0.1505224890767383</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05063291139240506</v>
+        <v>0.05128205128205128</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>82.74162197838049</v>
+        <v>80.10449781534766</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.1657701756037</v>
+        <v>91.41940904609683</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.23828411517193</v>
+        <v>26.08350787136052</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42411.82814790685</v>
+        <v>42156.70046800819</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.32852071469225</v>
+        <v>0.3376157882748987</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.17623872994889</v>
+        <v>31.98326124013237</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>52009.99811841829</v>
+        <v>51692.00288319917</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6291766445543741</v>
+        <v>0.6401672430837113</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5010,6 +5010,39 @@
       </c>
       <c r="I21">
         <f>IF(H21="","",IF(H21&gt;=70,"BUY",IF(H21&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B22" s="24" t="n">
+        <v>31516.3</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>0.150522489077</v>
+      </c>
+      <c r="F22" s="34">
+        <f>IF(D22="","",100*(1-D22))</f>
+        <v/>
+      </c>
+      <c r="G22" s="34">
+        <f>IF(E22="","",IF(E22&lt;=0,20,IF(E22&lt;5%,20+400*E22,IF(E22&lt;10%,40+400*(E22-5%),IF(E22&lt;15%,60+400*(E22-10%),IF(E22&lt;25%,80+200*(E22-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H22" s="34">
+        <f>IF(OR(F22="",G22=""),"",70%*F22+30%*G22)</f>
+        <v/>
+      </c>
+      <c r="I22">
+        <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31516.3</v>
+        <v>32422.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.5</v>
+        <v>20.06</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1616.220512820513</v>
+        <v>1616.276171485544</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1505224890767383</v>
+        <v>0.1506319503518214</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05128205128205128</v>
+        <v>0.04985044865403789</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.10449781534766</v>
+        <v>80.12639007036428</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.41940904609683</v>
+        <v>88.29164836439286</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.08350787136052</v>
+        <v>26.08579905222126</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42156.70046800819</v>
+        <v>42161.8554222654</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3376157882748987</v>
+        <v>0.3003887862523063</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.98326124013237</v>
+        <v>31.98400432581693</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51692.00288319917</v>
+        <v>51694.98406050845</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6401672430837113</v>
+        <v>0.5944169653946627</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5043,6 +5043,39 @@
       </c>
       <c r="I22">
         <f>IF(H22="","",IF(H22&gt;=70,"BUY",IF(H22&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B23" s="24" t="n">
+        <v>32422.5</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>0.150631950352</v>
+      </c>
+      <c r="F23" s="34">
+        <f>IF(D23="","",100*(1-D23))</f>
+        <v/>
+      </c>
+      <c r="G23" s="34">
+        <f>IF(E23="","",IF(E23&lt;=0,20,IF(E23&lt;5%,20+400*E23,IF(E23&lt;10%,40+400*(E23-5%),IF(E23&lt;15%,60+400*(E23-10%),IF(E23&lt;25%,80+200*(E23-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H23" s="34">
+        <f>IF(OR(F23="",G23=""),"",70%*F23+30%*G23)</f>
+        <v/>
+      </c>
+      <c r="I23">
+        <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>32422.5</v>
+        <v>32081.25</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>20.06</v>
+        <v>19.85</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.06716417910447761</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1616.276171485544</v>
+        <v>1616.183879093199</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1506319503518214</v>
+        <v>0.1505662471154068</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.04985044865403789</v>
+        <v>0.05037783375314861</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>93.28358208955224</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.12639007036428</v>
+        <v>80.11324942308136</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>88.29164836439286</v>
+        <v>89.33248228961097</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.08579905222126</v>
+        <v>26.08442378962134</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42161.8554222654</v>
+        <v>42157.22522422113</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3003887862523063</v>
+        <v>0.3140767652202183</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.98400432581693</v>
+        <v>31.98355829470345</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51694.98406050845</v>
+        <v>51691.31131193727</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.5944169653946627</v>
+        <v>0.6112623826047074</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5076,6 +5076,39 @@
       </c>
       <c r="I23">
         <f>IF(H23="","",IF(H23&gt;=70,"BUY",IF(H23&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B24" s="24" t="n">
+        <v>32081.25</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>0.0671641791045</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>0.150566247115</v>
+      </c>
+      <c r="F24" s="34">
+        <f>IF(D24="","",100*(1-D24))</f>
+        <v/>
+      </c>
+      <c r="G24" s="34">
+        <f>IF(E24="","",IF(E24&lt;=0,20,IF(E24&lt;5%,20+400*E24,IF(E24&lt;10%,40+400*(E24-5%),IF(E24&lt;15%,60+400*(E24-10%),IF(E24&lt;25%,80+200*(E24-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H24" s="34">
+        <f>IF(OR(F24="",G24=""),"",70%*F24+30%*G24)</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>32081.25</v>
+        <v>31995.5</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.85</v>
+        <v>19.79</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.06716417910447761</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1616.183879093199</v>
+        <v>1616.750884284992</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1505662471154068</v>
+        <v>0.1512163070758317</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05037783375314861</v>
+        <v>0.05053057099545225</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>93.28358208955224</v>
+        <v>94.02985074626866</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.11324942308136</v>
+        <v>80.24326141516633</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.33248228961097</v>
+        <v>89.89387394693796</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.08442378962134</v>
+        <v>26.09803047325012</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42157.22522422113</v>
+        <v>42194.01384572381</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3140767652202183</v>
+        <v>0.3187483816700416</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.98355829470345</v>
+        <v>31.98797127317765</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51691.31131193727</v>
+        <v>51716.5808423929</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6112623826047074</v>
+        <v>0.6163704534197902</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5109,6 +5109,39 @@
       </c>
       <c r="I24">
         <f>IF(H24="","",IF(H24&gt;=70,"BUY",IF(H24&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B25" s="24" t="n">
+        <v>31995.5</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>19.79</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0.0597014925373</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0.151216307076</v>
+      </c>
+      <c r="F25" s="34">
+        <f>IF(D25="","",100*(1-D25))</f>
+        <v/>
+      </c>
+      <c r="G25" s="34">
+        <f>IF(E25="","",IF(E25&lt;=0,20,IF(E25&lt;5%,20+400*E25,IF(E25&lt;10%,40+400*(E25-5%),IF(E25&lt;15%,60+400*(E25-10%),IF(E25&lt;25%,80+200*(E25-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H25" s="34">
+        <f>IF(OR(F25="",G25=""),"",70%*F25+30%*G25)</f>
+        <v/>
+      </c>
+      <c r="I25">
+        <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31995.5</v>
+        <v>32273.05</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.79</v>
+        <v>19.97</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05970149253731343</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1616.750884284992</v>
+        <v>1616.076614922384</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1512163070758317</v>
+        <v>0.1505441055931338</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05053057099545225</v>
+        <v>0.05007511266900351</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.02985074626866</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.24326141516633</v>
+        <v>80.10882111862676</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>89.89387394693796</v>
+        <v>88.2863776788716</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.09803047325012</v>
+        <v>26.08396033592943</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42194.01384572381</v>
+        <v>42153.67832345855</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3187483816700416</v>
+        <v>0.3061572526754845</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.98797127317765</v>
+        <v>31.98340798539796</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51716.5808423929</v>
+        <v>51687.63771072347</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6163704534197902</v>
+        <v>0.6015727584075092</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5142,6 +5142,39 @@
       </c>
       <c r="I25">
         <f>IF(H25="","",IF(H25&gt;=70,"BUY",IF(H25&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B26" s="24" t="n">
+        <v>32273.05</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0.150544105593</v>
+      </c>
+      <c r="F26" s="34">
+        <f>IF(D26="","",100*(1-D26))</f>
+        <v/>
+      </c>
+      <c r="G26" s="34">
+        <f>IF(E26="","",IF(E26&lt;=0,20,IF(E26&lt;5%,20+400*E26,IF(E26&lt;10%,40+400*(E26-5%),IF(E26&lt;15%,60+400*(E26-10%),IF(E26&lt;25%,80+200*(E26-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H26" s="34">
+        <f>IF(OR(F26="",G26=""),"",70%*F26+30%*G26)</f>
+        <v/>
+      </c>
+      <c r="I26">
+        <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>32273.05</v>
+        <v>32189.45</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.97</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.08208955223880597</v>
+        <v>0.05223880597014925</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1616.076614922384</v>
+        <v>1632.325050709939</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1505441055931338</v>
+        <v>0.1566167244181131</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05007511266900351</v>
+        <v>0.05070993914807303</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>91.79104477611941</v>
+        <v>94.77611940298507</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>80.10882111862676</v>
+        <v>81.32334488362262</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>88.2863776788716</v>
+        <v>90.74028704717634</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.08396033592943</v>
+        <v>26.21020222869573</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42153.67832345855</v>
+        <v>42783.56968207352</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3061572526754845</v>
+        <v>0.3291177600758484</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>31.98340798539796</v>
+        <v>32.06792288211209</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>51687.63771072347</v>
+        <v>52345.27384470604</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6015727584075092</v>
+        <v>0.6261624179570027</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5175,6 +5175,39 @@
       </c>
       <c r="I26">
         <f>IF(H26="","",IF(H26&gt;=70,"BUY",IF(H26&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B27" s="24" t="n">
+        <v>32189.45</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0.0522388059701</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>0.156616724418</v>
+      </c>
+      <c r="F27" s="34">
+        <f>IF(D27="","",100*(1-D27))</f>
+        <v/>
+      </c>
+      <c r="G27" s="34">
+        <f>IF(E27="","",IF(E27&lt;=0,20,IF(E27&lt;5%,20+400*E27,IF(E27&lt;10%,40+400*(E27-5%),IF(E27&lt;15%,60+400*(E27-10%),IF(E27&lt;25%,80+200*(E27-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H27" s="34">
+        <f>IF(OR(F27="",G27=""),"",70%*F27+30%*G27)</f>
+        <v/>
+      </c>
+      <c r="I27">
+        <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>32189.45</v>
+        <v>31553.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.72</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.05223880597014925</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1632.325050709939</v>
+        <v>1631.509824198552</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1566167244181131</v>
+        <v>0.1560569495288733</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05070993914807303</v>
+        <v>0.05170630816959669</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>94.77611940298507</v>
+        <v>96.26865671641791</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>81.32334488362262</v>
+        <v>81.21138990577465</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>90.74028704717634</v>
+        <v>91.75147667322493</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.21020222869573</v>
+        <v>26.19935203499579</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42783.56968207352</v>
+        <v>42744.50023273196</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3291177600758484</v>
+        <v>0.3546717701652424</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.06792288211209</v>
+        <v>32.05937272051816</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>52345.27384470604</v>
+        <v>52305.18155116843</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6261624179570027</v>
+        <v>0.6576718056110731</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5208,6 +5208,39 @@
       </c>
       <c r="I27">
         <f>IF(H27="","",IF(H27&gt;=70,"BUY",IF(H27&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B28" s="24" t="n">
+        <v>31553.4</v>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>0.156056949529</v>
+      </c>
+      <c r="F28" s="34">
+        <f>IF(D28="","",100*(1-D28))</f>
+        <v/>
+      </c>
+      <c r="G28" s="34">
+        <f>IF(E28="","",IF(E28&lt;=0,20,IF(E28&lt;5%,20+400*E28,IF(E28&lt;10%,40+400*(E28-5%),IF(E28&lt;15%,60+400*(E28-10%),IF(E28&lt;25%,80+200*(E28-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H28" s="34">
+        <f>IF(OR(F28="",G28=""),"",70%*F28+30%*G28)</f>
+        <v/>
+      </c>
+      <c r="I28">
+        <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31553.4</v>
+        <v>31866.4</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.34</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1631.509824198552</v>
+        <v>1631.664106502816</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1560569495288733</v>
+        <v>0.1560414408183133</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05170630816959669</v>
+        <v>0.05120327700972862</v>
       </c>
     </row>
     <row r="8">
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>81.21138990577465</v>
+        <v>81.20828816366266</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.75147667322493</v>
+        <v>91.75054615059133</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.19935203499579</v>
+        <v>26.19902741552847</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42744.50023273196</v>
+        <v>42748.01265920104</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3546717701652424</v>
+        <v>0.3414760581427787</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.05937272051816</v>
+        <v>32.059135836042</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>52305.18155116843</v>
+        <v>52309.74122916789</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6576718056110731</v>
+        <v>0.6415328129053766</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5241,6 +5241,39 @@
       </c>
       <c r="I28">
         <f>IF(H28="","",IF(H28&gt;=70,"BUY",IF(H28&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B29" s="24" t="n">
+        <v>31866.4</v>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>0.0373134328358</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>0.156041440818</v>
+      </c>
+      <c r="F29" s="34">
+        <f>IF(D29="","",100*(1-D29))</f>
+        <v/>
+      </c>
+      <c r="G29" s="34">
+        <f>IF(E29="","",IF(E29&lt;=0,20,IF(E29&lt;5%,20+400*E29,IF(E29&lt;10%,40+400*(E29-5%),IF(E29&lt;15%,60+400*(E29-10%),IF(E29&lt;25%,80+200*(E29-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H29" s="34">
+        <f>IF(OR(F29="",G29=""),"",70%*F29+30%*G29)</f>
+        <v/>
+      </c>
+      <c r="I29">
+        <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>

--- a/docs/downloads/indices/nifty-it.xlsx
+++ b/docs/downloads/indices/nifty-it.xlsx
@@ -570,7 +570,7 @@
     <col width="34" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
   </cols>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B2" s="23" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>31866.4</v>
+        <v>32606.9</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="E5" s="25" t="n">
-        <v>19.53</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="6">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.08208955223880597</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="E6" s="27" t="n">
-        <v>1631.664106502816</v>
+        <v>1631.976976976977</v>
       </c>
     </row>
     <row r="7">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>0.1560414408183133</v>
+        <v>0.1562700324815158</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.05120327700972862</v>
+        <v>0.05005005005005005</v>
       </c>
     </row>
     <row r="8">
@@ -670,7 +670,7 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>96.26865671641791</v>
+        <v>91.79104477611941</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -678,7 +678,7 @@
         </is>
       </c>
       <c r="E8" s="28" t="n">
-        <v>81.20828816366266</v>
+        <v>81.25400649630316</v>
       </c>
     </row>
     <row r="9">
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="B9" s="28" t="n">
-        <v>91.75054615059133</v>
+        <v>88.62993329217453</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
@@ -737,13 +737,13 @@
         </is>
       </c>
       <c r="B13" s="29" t="n">
-        <v>26.19902741552847</v>
+        <v>26.20381216559882</v>
       </c>
       <c r="C13" s="15" t="n">
-        <v>42748.01265920104</v>
+        <v>42764.0181632865</v>
       </c>
       <c r="D13" s="30" t="n">
-        <v>0.3414760581427787</v>
+        <v>0.3115021103903315</v>
       </c>
     </row>
     <row r="14">
@@ -753,13 +753,13 @@
         </is>
       </c>
       <c r="B14" s="29" t="n">
-        <v>32.059135836042</v>
+        <v>32.06262741041766</v>
       </c>
       <c r="C14" s="15" t="n">
-        <v>52309.74122916789</v>
+        <v>52325.46975519258</v>
       </c>
       <c r="D14" s="30" t="n">
-        <v>0.6415328129053766</v>
+        <v>0.6047361066275105</v>
       </c>
     </row>
     <row r="16">
@@ -4292,7 +4292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -5274,6 +5274,39 @@
       </c>
       <c r="I29">
         <f>IF(H29="","",IF(H29&gt;=70,"BUY",IF(H29&gt;=40,"HOLD","SELL")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="31" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B30" s="24" t="n">
+        <v>32606.9</v>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>0.0820895522388</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>0.156270032482</v>
+      </c>
+      <c r="F30" s="34">
+        <f>IF(D30="","",100*(1-D30))</f>
+        <v/>
+      </c>
+      <c r="G30" s="34">
+        <f>IF(E30="","",IF(E30&lt;=0,20,IF(E30&lt;5%,20+400*E30,IF(E30&lt;10%,40+400*(E30-5%),IF(E30&lt;15%,60+400*(E30-10%),IF(E30&lt;25%,80+200*(E30-15%),100))))))</f>
+        <v/>
+      </c>
+      <c r="H30" s="34">
+        <f>IF(OR(F30="",G30=""),"",70%*F30+30%*G30)</f>
+        <v/>
+      </c>
+      <c r="I30">
+        <f>IF(H30="","",IF(H30&gt;=70,"BUY",IF(H30&gt;=40,"HOLD","SELL")))</f>
         <v/>
       </c>
     </row>
@@ -5314,7 +5347,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -5394,7 +5427,7 @@
         </is>
       </c>
       <c r="E6" s="37" t="n">
-        <v>0.313</v>
+        <v>0.317</v>
       </c>
     </row>
     <row r="7">
@@ -5417,7 +5450,7 @@
         </is>
       </c>
       <c r="E7" s="37" t="n">
-        <v>0.1908</v>
+        <v>0.1978</v>
       </c>
     </row>
     <row r="8">
@@ -5440,7 +5473,7 @@
         </is>
       </c>
       <c r="E8" s="37" t="n">
-        <v>0.1181</v>
+        <v>0.1165</v>
       </c>
     </row>
     <row r="9">
@@ -5463,7 +5496,7 @@
         </is>
       </c>
       <c r="E9" s="37" t="n">
-        <v>0.1047</v>
+        <v>0.1046</v>
       </c>
     </row>
     <row r="10">
@@ -5486,7 +5519,7 @@
         </is>
       </c>
       <c r="E10" s="37" t="n">
-        <v>0.0659</v>
+        <v>0.0655</v>
       </c>
     </row>
     <row r="11">
@@ -5509,7 +5542,7 @@
         </is>
       </c>
       <c r="E11" s="37" t="n">
-        <v>0.0621</v>
+        <v>0.0605</v>
       </c>
     </row>
     <row r="12">
@@ -5532,7 +5565,7 @@
         </is>
       </c>
       <c r="E12" s="37" t="n">
-        <v>0.0464</v>
+        <v>0.04940000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -5555,7 +5588,7 @@
         </is>
       </c>
       <c r="E13" s="37" t="n">
-        <v>0.0406</v>
+        <v>0.0361</v>
       </c>
     </row>
     <row r="14">
@@ -5578,7 +5611,7 @@
         </is>
       </c>
       <c r="E14" s="37" t="n">
-        <v>0.0309</v>
+        <v>0.0307</v>
       </c>
     </row>
     <row r="15">
@@ -5601,7 +5634,7 @@
         </is>
       </c>
       <c r="E15" s="37" t="n">
-        <v>0.0275</v>
+        <v>0.0219</v>
       </c>
     </row>
   </sheetData>
